--- a/output/pdf_financials_xlsx/AAG.xlsx
+++ b/output/pdf_financials_xlsx/AAG.xlsx
@@ -5100,43 +5100,43 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.550939</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.578524</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.635856</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.70843</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.70843</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.70843</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.70843</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.040235</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.351178</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.942829</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.510352</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.71162</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.084295</v>
       </c>
     </row>
     <row r="93">
@@ -8684,7 +8684,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11236,7 +11240,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -12012,7 +12020,11 @@
           <t>Share-based payments reserve (note 5(d))</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -12680,7 +12692,11 @@
           <t>Share-based payments reserve (note 6(d))</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -13524,7 +13540,11 @@
           <t>Share-based payments reserve (note 6(d))</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -14358,7 +14378,11 @@
           <t>Share-based payment reserve (note 6(d))</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AAG.xlsx
+++ b/output/pdf_financials_xlsx/AAG.xlsx
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.07810400000000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.296197</v>
       </c>
     </row>
     <row r="13">
@@ -1766,10 +1766,10 @@
         <v>-8.499243999999999</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-7.121868</v>
+        <v>-7.199972</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-14.162591</v>
+        <v>-14.458788</v>
       </c>
     </row>
     <row r="28">
@@ -1864,10 +1864,10 @@
         <v>-8.482441</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.108979</v>
+        <v>-7.187083</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-14.147907</v>
+        <v>-14.444104</v>
       </c>
     </row>
     <row r="30">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.017042</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.142255</v>
@@ -2099,34 +2099,34 @@
         <v>0.120862</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005828</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.232902</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.043323</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.965675</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>11.737858</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.827121</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.089832</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.331365</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>8.618745000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.017042</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.142255</v>
@@ -2197,34 +2197,34 @@
         <v>0.120862</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005828</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.232902</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.043323</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.965675</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>11.737858</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.827121</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.089832</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.331365</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>8.618745000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.041885</v>
+        <v>0.024843</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.007212</v>
@@ -2785,34 +2785,34 @@
         <v>0.00074</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.007085</v>
+        <v>0.001257</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001799</v>
+        <v>0.001257</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.289886</v>
+        <v>0.056984</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.043925</v>
+        <v>0.000602</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.087158</v>
+        <v>0.121483</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>11.88081</v>
+        <v>0.142952</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.971556</v>
+        <v>0.144435</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.411423</v>
+        <v>2.321591</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.483715</v>
+        <v>0.15235</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>13.900796</v>
+        <v>5.282051</v>
       </c>
     </row>
     <row r="49">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -26524,7 +26524,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">

--- a/output/pdf_financials_xlsx/AAG.xlsx
+++ b/output/pdf_financials_xlsx/AAG.xlsx
@@ -697,13 +697,13 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.214705</v>
+        <v>0.268705</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.101994</v>
+        <v>0.131994</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.09268899999999999</v>
+        <v>0.096689</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.001507</v>
@@ -715,25 +715,25 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.18</v>
+        <v>0.207</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.862341</v>
+        <v>0.8983409999999999</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.369529</v>
+        <v>1.419529</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.693062</v>
+        <v>0.781812</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.9241279999999999</v>
+        <v>1.014128</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.066567</v>
+        <v>1.156567</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.12304</v>
+        <v>1.22304</v>
       </c>
     </row>
     <row r="8">
@@ -1208,7 +1208,7 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.040306</v>
+        <v>-0.040306</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -5524,16 +5524,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000677</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.045842</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.036435</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.008513</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>-0.003429</v>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.031679</v>
+        <v>0.031002</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-1.907257</v>
@@ -5989,22 +5989,22 @@
         <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.062136</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.641232</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>1.15573</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>1.132533</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.792863</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.7003549999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6044,16 +6044,16 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.062847</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01103</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01314</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015683</v>
       </c>
     </row>
     <row r="112">
@@ -7215,16 +7215,16 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.062847</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01103</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01314</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015683</v>
       </c>
     </row>
     <row r="135">
@@ -7268,16 +7268,16 @@
         <v>-3.820937</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-5.889085</v>
+        <v>-5.951932</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-5.68006</v>
+        <v>-5.69109</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-5.406069</v>
+        <v>-5.419209</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-11.30537</v>
+        <v>-11.321053</v>
       </c>
     </row>
   </sheetData>
@@ -7291,7 +7291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R462"/>
+  <dimension ref="A1:R466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15134,7 +15134,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -16008,7 +16012,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -17986,7 +17994,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -19698,7 +19710,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -22562,7 +22578,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -23326,7 +23346,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="n">
         <v>-0.000677</v>
       </c>
@@ -24933,24 +24957,26 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Accounting and legal (note 10) $</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for cash</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24997,40 +25023,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O211" s="5" t="n">
-        <v>0.172886</v>
-      </c>
-      <c r="P211" s="5" t="n">
-        <v>0.206195</v>
-      </c>
-      <c r="Q211" s="5" t="n">
-        <v>0.212718</v>
-      </c>
-      <c r="R211" s="5" t="n">
-        <v>0.197877</v>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Accretion expense (note 7)</t>
+          <t>Net cash flow for the period and cash at year end $</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E212" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25087,11 +25119,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q212" s="5" t="n">
-        <v>0.792863</v>
-      </c>
-      <c r="R212" s="5" t="n">
-        <v>0.7003549999999999</v>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -25107,7 +25143,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Conference and exhibition</t>
+          <t>Accounting and legal (note 10) $</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -25116,14 +25152,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F213" s="5" t="n">
-        <v>0.007545</v>
-      </c>
-      <c r="G213" s="5" t="n">
-        <v>0.012936</v>
-      </c>
-      <c r="H213" s="5" t="n">
-        <v>0.006217</v>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -25145,23 +25187,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M213" s="5" t="n">
-        <v>0.07981199999999999</v>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v>0.012878</v>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O213" s="5" t="n">
-        <v>0.081759</v>
+        <v>0.172886</v>
       </c>
       <c r="P213" s="5" t="n">
-        <v>0.08673599999999999</v>
+        <v>0.206195</v>
       </c>
       <c r="Q213" s="5" t="n">
-        <v>0.106786</v>
+        <v>0.212718</v>
       </c>
       <c r="R213" s="5" t="n">
-        <v>0.295504</v>
+        <v>0.197877</v>
       </c>
     </row>
     <row r="214">
@@ -25177,14 +25223,10 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Consulting fees (note 10)</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accretion expense (note 7)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -25235,17 +25277,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O214" s="5" t="n">
-        <v>0.328244</v>
-      </c>
-      <c r="P214" s="5" t="n">
-        <v>0.365093</v>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q214" s="5" t="n">
-        <v>0.205344</v>
+        <v>0.792863</v>
       </c>
       <c r="R214" s="5" t="n">
-        <v>0.635871</v>
+        <v>0.7003549999999999</v>
       </c>
     </row>
     <row r="215">
@@ -25261,7 +25307,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Corporate secretarial (note 10)</t>
+          <t>Conference and exhibition</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -25270,20 +25316,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F215" s="5" t="n">
+        <v>0.007545</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>0.012936</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>0.006217</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -25305,27 +25345,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M215" s="5" t="n">
+        <v>0.07981199999999999</v>
+      </c>
+      <c r="N215" s="5" t="n">
+        <v>0.012878</v>
       </c>
       <c r="O215" s="5" t="n">
-        <v>0.033</v>
+        <v>0.081759</v>
       </c>
       <c r="P215" s="5" t="n">
-        <v>0.033</v>
+        <v>0.08673599999999999</v>
       </c>
       <c r="Q215" s="5" t="n">
-        <v>0.033</v>
+        <v>0.106786</v>
       </c>
       <c r="R215" s="5" t="n">
-        <v>0.037</v>
+        <v>0.295504</v>
       </c>
     </row>
     <row r="216">
@@ -25341,12 +25377,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Depreciation (note 8)</t>
+          <t>Consulting fees (note 10)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -25399,21 +25435,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O216" s="5" t="n">
+        <v>0.328244</v>
+      </c>
+      <c r="P216" s="5" t="n">
+        <v>0.365093</v>
       </c>
       <c r="Q216" s="5" t="n">
-        <v>0.012889</v>
+        <v>0.205344</v>
       </c>
       <c r="R216" s="5" t="n">
-        <v>0.014684</v>
+        <v>0.635871</v>
       </c>
     </row>
     <row r="217">
@@ -25429,7 +25461,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Directors’ fees (note 10)</t>
+          <t>Corporate secretarial (note 10)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -25484,16 +25516,16 @@
         </is>
       </c>
       <c r="O217" s="5" t="n">
-        <v>0.08875</v>
+        <v>0.033</v>
       </c>
       <c r="P217" s="5" t="n">
-        <v>0.09</v>
+        <v>0.033</v>
       </c>
       <c r="Q217" s="5" t="n">
-        <v>0.09</v>
+        <v>0.033</v>
       </c>
       <c r="R217" s="5" t="n">
-        <v>0.1</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="218">
@@ -25509,12 +25541,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Depreciation (note 8)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -25578,10 +25610,10 @@
         </is>
       </c>
       <c r="Q218" s="5" t="n">
-        <v>0.031867</v>
+        <v>0.012889</v>
       </c>
       <c r="R218" s="5" t="n">
-        <v>0.400748</v>
+        <v>0.014684</v>
       </c>
     </row>
     <row r="219">
@@ -25597,10 +25629,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Geological exploration (note 6)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Directors’ fees (note 10)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -25651,21 +25687,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O219" s="5" t="n">
+        <v>0.08875</v>
+      </c>
+      <c r="P219" s="5" t="n">
+        <v>0.09</v>
       </c>
       <c r="Q219" s="5" t="n">
-        <v>0.758876</v>
+        <v>0.09</v>
       </c>
       <c r="R219" s="5" t="n">
-        <v>0.838655</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="220">
@@ -25681,12 +25713,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -25694,17 +25726,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F220" s="5" t="n">
-        <v>0.036147</v>
-      </c>
-      <c r="G220" s="5" t="n">
-        <v>0.028577</v>
-      </c>
-      <c r="H220" s="5" t="n">
-        <v>0.032992</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>0.001231</v>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -25721,23 +25761,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M220" s="5" t="n">
-        <v>0.006667</v>
-      </c>
-      <c r="N220" s="5" t="n">
-        <v>0.015282</v>
-      </c>
-      <c r="O220" s="5" t="n">
-        <v>0.016427</v>
-      </c>
-      <c r="P220" s="5" t="n">
-        <v>0.01785</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q220" s="5" t="n">
-        <v>0.016975</v>
+        <v>0.031867</v>
       </c>
       <c r="R220" s="5" t="n">
-        <v>0.019386</v>
+        <v>0.400748</v>
       </c>
     </row>
     <row r="221">
@@ -25753,27 +25801,29 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Geological exploration (note 6)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F221" s="5" t="n">
-        <v>0.177008</v>
-      </c>
-      <c r="G221" s="5" t="n">
-        <v>0.071479</v>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>0.058253</v>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -25795,23 +25845,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M221" s="5" t="n">
-        <v>0.57517</v>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v>0.540964</v>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v>0.348391</v>
-      </c>
-      <c r="P221" s="5" t="n">
-        <v>0.541185</v>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q221" s="5" t="n">
-        <v>0.844248</v>
+        <v>0.758876</v>
       </c>
       <c r="R221" s="5" t="n">
-        <v>0.467783</v>
+        <v>0.838655</v>
       </c>
     </row>
     <row r="222">
@@ -25827,12 +25885,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -25841,43 +25899,49 @@
         </is>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.025285</v>
+        <v>0.036147</v>
       </c>
       <c r="G222" s="5" t="n">
-        <v>0.017002</v>
+        <v>0.028577</v>
       </c>
       <c r="H222" s="5" t="n">
-        <v>0.027016</v>
+        <v>0.032992</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>0.005208</v>
-      </c>
-      <c r="J222" s="5" t="n">
-        <v>0.029999</v>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>0.013373</v>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v>0.012678</v>
+        <v>0.001231</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M222" s="5" t="n">
-        <v>0.050285</v>
+        <v>0.006667</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>0.114418</v>
+        <v>0.015282</v>
       </c>
       <c r="O222" s="5" t="n">
-        <v>0.066417</v>
+        <v>0.016427</v>
       </c>
       <c r="P222" s="5" t="n">
-        <v>0.109025</v>
+        <v>0.01785</v>
       </c>
       <c r="Q222" s="5" t="n">
-        <v>0.071913</v>
+        <v>0.016975</v>
       </c>
       <c r="R222" s="5" t="n">
-        <v>0.063987</v>
+        <v>0.019386</v>
       </c>
     </row>
     <row r="223">
@@ -25893,29 +25957,27 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Office and sundry (note 10)</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F223" s="5" t="n">
+        <v>0.177008</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>0.071479</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>0.058253</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -25937,27 +25999,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M223" s="5" t="n">
+        <v>0.57517</v>
+      </c>
+      <c r="N223" s="5" t="n">
+        <v>0.540964</v>
       </c>
       <c r="O223" s="5" t="n">
-        <v>0.125052</v>
+        <v>0.348391</v>
       </c>
       <c r="P223" s="5" t="n">
-        <v>0.158194</v>
+        <v>0.541185</v>
       </c>
       <c r="Q223" s="5" t="n">
-        <v>0.134937</v>
+        <v>0.844248</v>
       </c>
       <c r="R223" s="5" t="n">
-        <v>0.141769</v>
+        <v>0.467783</v>
       </c>
     </row>
     <row r="224">
@@ -25973,75 +26031,57 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Pre-acquisition exploration (notes 7 and 10)</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F224" s="5" t="n">
+        <v>0.025285</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>0.017002</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>0.027016</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>0.005208</v>
+      </c>
+      <c r="J224" s="5" t="n">
+        <v>0.029999</v>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>0.013373</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>0.012678</v>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>0.050285</v>
+      </c>
+      <c r="N224" s="5" t="n">
+        <v>0.114418</v>
+      </c>
+      <c r="O224" s="5" t="n">
+        <v>0.066417</v>
+      </c>
+      <c r="P224" s="5" t="n">
+        <v>0.109025</v>
       </c>
       <c r="Q224" s="5" t="n">
-        <v>2.936359</v>
+        <v>0.071913</v>
       </c>
       <c r="R224" s="5" t="n">
-        <v>8.18628</v>
+        <v>0.063987</v>
       </c>
     </row>
     <row r="225">
@@ -26057,7 +26097,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Share-based payments (notes 9 and 10)</t>
+          <t>Office and sundry (note 10)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -26112,16 +26152,16 @@
         </is>
       </c>
       <c r="O225" s="5" t="n">
-        <v>0.793314</v>
+        <v>0.125052</v>
       </c>
       <c r="P225" s="5" t="n">
-        <v>0.548686</v>
+        <v>0.158194</v>
       </c>
       <c r="Q225" s="5" t="n">
-        <v>0.193647</v>
+        <v>0.134937</v>
       </c>
       <c r="R225" s="5" t="n">
-        <v>1.624031</v>
+        <v>0.141769</v>
       </c>
     </row>
     <row r="226">
@@ -26137,7 +26177,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Travel and meals</t>
+          <t>Pre-acquisition exploration (notes 7 and 10)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -26146,14 +26186,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F226" s="5" t="n">
-        <v>0.086371</v>
-      </c>
-      <c r="G226" s="5" t="n">
-        <v>0.052181</v>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>0.069754</v>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -26165,29 +26211,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K226" s="5" t="n">
-        <v>0.006484</v>
-      </c>
-      <c r="L226" s="5" t="n">
-        <v>0.107283</v>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v>0.133864</v>
-      </c>
-      <c r="N226" s="5" t="n">
-        <v>0.008163999999999999</v>
-      </c>
-      <c r="O226" s="5" t="n">
-        <v>0.131213</v>
-      </c>
-      <c r="P226" s="5" t="n">
-        <v>0.166735</v>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q226" s="5" t="n">
-        <v>0.320143</v>
+        <v>2.936359</v>
       </c>
       <c r="R226" s="5" t="n">
-        <v>0.349982</v>
+        <v>8.18628</v>
       </c>
     </row>
     <row r="227">
@@ -26203,7 +26261,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Wages and salaries (note 10)</t>
+          <t>Share-based payments (notes 9 and 10)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -26258,16 +26316,16 @@
         </is>
       </c>
       <c r="O227" s="5" t="n">
-        <v>0.248624</v>
+        <v>0.793314</v>
       </c>
       <c r="P227" s="5" t="n">
-        <v>0.249196</v>
+        <v>0.548686</v>
       </c>
       <c r="Q227" s="5" t="n">
-        <v>0.248376</v>
+        <v>0.193647</v>
       </c>
       <c r="R227" s="5" t="n">
-        <v>0.351879</v>
+        <v>1.624031</v>
       </c>
     </row>
     <row r="228">
@@ -26283,55 +26341,57 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E228" s="5" t="n">
-        <v>1e-06</v>
+          <t>Travel and meals</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F228" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.086371</v>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1.147721</v>
+        <v>0.052181</v>
       </c>
       <c r="H228" s="5" t="n">
-        <v>0.553312</v>
-      </c>
-      <c r="I228" s="5" t="n">
-        <v>0.200455</v>
-      </c>
-      <c r="J228" s="5" t="n">
-        <v>0.284765</v>
+        <v>0.069754</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K228" s="5" t="n">
-        <v>0.453582</v>
+        <v>0.006484</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>0.570663</v>
+        <v>0.107283</v>
       </c>
       <c r="M228" s="5" t="n">
-        <v>3.427801</v>
+        <v>0.133864</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>7.022248</v>
+        <v>0.008163999999999999</v>
       </c>
       <c r="O228" s="5" t="n">
-        <v>8.771061</v>
+        <v>0.131213</v>
       </c>
       <c r="P228" s="5" t="n">
-        <v>7.883226</v>
+        <v>0.166735</v>
       </c>
       <c r="Q228" s="5" t="n">
-        <v>7.010941</v>
+        <v>0.320143</v>
       </c>
       <c r="R228" s="5" t="n">
-        <v>14.425791</v>
+        <v>0.349982</v>
       </c>
     </row>
     <row r="229">
@@ -26347,7 +26407,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Impairment to assets held for sale (note 5)</t>
+          <t>Wages and salaries (note 10)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -26401,23 +26461,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O229" s="5" t="n">
+        <v>0.248624</v>
+      </c>
+      <c r="P229" s="5" t="n">
+        <v>0.249196</v>
       </c>
       <c r="Q229" s="5" t="n">
-        <v>-0.189031</v>
-      </c>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.248376</v>
+      </c>
+      <c r="R229" s="5" t="n">
+        <v>0.351879</v>
       </c>
     </row>
     <row r="230">
@@ -26433,77 +26487,55 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Loss on modification of acquisition costs payable</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F230" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>1.147721</v>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>0.553312</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>0.200455</v>
+      </c>
+      <c r="J230" s="5" t="n">
+        <v>0.284765</v>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>0.453582</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>0.570663</v>
+      </c>
+      <c r="M230" s="5" t="n">
+        <v>3.427801</v>
+      </c>
+      <c r="N230" s="5" t="n">
+        <v>7.022248</v>
+      </c>
+      <c r="O230" s="5" t="n">
+        <v>8.771061</v>
+      </c>
+      <c r="P230" s="5" t="n">
+        <v>7.883226</v>
+      </c>
+      <c r="Q230" s="5" t="n">
+        <v>7.010941</v>
       </c>
       <c r="R230" s="5" t="n">
-        <v>-0.032997</v>
+        <v>14.425791</v>
       </c>
     </row>
     <row r="231">
@@ -26519,14 +26551,10 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Impairment to assets held for sale (note 5)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -26588,10 +26616,12 @@
         </is>
       </c>
       <c r="Q231" s="5" t="n">
-        <v>0.07810400000000001</v>
-      </c>
-      <c r="R231" s="5" t="n">
-        <v>0.296197</v>
+        <v>-0.189031</v>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -26607,14 +26637,10 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Loss and Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss on modification of acquisition costs payable</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -26655,23 +26681,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M232" s="5" t="n">
-        <v>-3.040474</v>
-      </c>
-      <c r="N232" s="5" t="n">
-        <v>-6.899208</v>
-      </c>
-      <c r="O232" s="5" t="n">
-        <v>-8.771061</v>
-      </c>
-      <c r="P232" s="5" t="n">
-        <v>-8.499243999999999</v>
-      </c>
-      <c r="Q232" s="5" t="n">
-        <v>-7.121868</v>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R232" s="5" t="n">
-        <v>-14.162591</v>
+        <v>-0.032997</v>
       </c>
     </row>
     <row r="233">
@@ -26687,12 +26723,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -26740,20 +26776,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N233" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="O233" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="P233" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q233" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.07810400000000001</v>
       </c>
       <c r="R233" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.296197</v>
       </c>
     </row>
     <row r="234">
@@ -26764,15 +26806,19 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding -</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Loss and Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -26813,27 +26859,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M234" s="5" t="n">
+        <v>-3.040474</v>
+      </c>
+      <c r="N234" s="5" t="n">
+        <v>-6.899208</v>
       </c>
       <c r="O234" s="5" t="n">
-        <v>135.814199</v>
+        <v>-8.771061</v>
       </c>
       <c r="P234" s="5" t="n">
-        <v>159.404203</v>
+        <v>-8.499243999999999</v>
       </c>
       <c r="Q234" s="5" t="n">
-        <v>210.176094</v>
+        <v>-7.121868</v>
       </c>
       <c r="R234" s="5" t="n">
-        <v>268.032433</v>
+        <v>-14.162591</v>
       </c>
     </row>
     <row r="235">
@@ -26844,15 +26886,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>May 31, 2023 207,283,011 $ 53,589,975 $ 6,510,352 $ - $</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -26898,26 +26944,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N235" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="O235" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="P235" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="Q235" s="5" t="n">
-        <v>25.064078</v>
+        <v>-3e-08</v>
       </c>
       <c r="R235" s="5" t="n">
-        <v>-35.036249</v>
+        <v>-5e-08</v>
       </c>
     </row>
     <row r="236">
@@ -26928,12 +26968,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
+          <t>Weighted average number of shares outstanding -</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Private placements 17,500,000 3,850,000 - -</t>
+          <t>Weighted average number of shares outstanding - basic and diluted</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -26987,21 +27027,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O236" s="5" t="n">
+        <v>135.814199</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>3.85</v>
+        <v>159.404203</v>
       </c>
       <c r="Q236" s="5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>210.176094</v>
+      </c>
+      <c r="R236" s="5" t="n">
+        <v>268.032433</v>
       </c>
     </row>
     <row r="237">
@@ -27017,7 +27053,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Warrants exercised 8,308,398 2,095,820 - -</t>
+          <t>May 31, 2023 207,283,011 $ 53,589,975 $ 6,510,352 $ - $</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -27076,16 +27112,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P237" s="5" t="n">
-        <v>2.09582</v>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q237" s="5" t="n">
-        <v>2.09582</v>
-      </c>
-      <c r="R237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.064078</v>
+      </c>
+      <c r="R237" s="5" t="n">
+        <v>-35.036249</v>
       </c>
     </row>
     <row r="238">
@@ -27101,7 +27137,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Options exercised 169,500 102,359 (45,576) -</t>
+          <t>Private placements 17,500,000 3,850,000 - -</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -27161,10 +27197,10 @@
         </is>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.056783</v>
+        <v>3.85</v>
       </c>
       <c r="Q238" s="5" t="n">
-        <v>0.056783</v>
+        <v>3.85</v>
       </c>
       <c r="R238" t="inlineStr">
         <is>
@@ -27185,7 +27221,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (233,775) - -</t>
+          <t>Warrants exercised 8,308,398 2,095,820 - -</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -27245,10 +27281,10 @@
         </is>
       </c>
       <c r="P239" s="5" t="n">
-        <v>-0.233775</v>
+        <v>2.09582</v>
       </c>
       <c r="Q239" s="5" t="n">
-        <v>-0.233775</v>
+        <v>2.09582</v>
       </c>
       <c r="R239" t="inlineStr">
         <is>
@@ -27269,7 +27305,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ warrants - (53,197) 53,197 -</t>
+          <t>Options exercised 169,500 102,359 (45,576) -</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -27328,15 +27364,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P240" s="5" t="n">
+        <v>0.056783</v>
+      </c>
+      <c r="Q240" s="5" t="n">
+        <v>0.056783</v>
       </c>
       <c r="R240" t="inlineStr">
         <is>
@@ -27357,7 +27389,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance - - - 14,000</t>
+          <t>Share issuance costs – cash - (233,775) - -</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -27417,10 +27449,10 @@
         </is>
       </c>
       <c r="P241" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.233775</v>
       </c>
       <c r="Q241" s="5" t="n">
-        <v>0.014</v>
+        <v>-0.233775</v>
       </c>
       <c r="R241" t="inlineStr">
         <is>
@@ -27441,7 +27473,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Share-based payments - - 193,647 -</t>
+          <t>Share issuance costs – finders’ warrants - (53,197) 53,197 -</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -27500,11 +27532,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P242" s="5" t="n">
-        <v>0.193647</v>
-      </c>
-      <c r="Q242" s="5" t="n">
-        <v>0.193647</v>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
@@ -27525,14 +27561,10 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Subscriptions received in advance - - - 14,000</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27589,13 +27621,15 @@
         </is>
       </c>
       <c r="P243" s="5" t="n">
-        <v>-8.499243999999999</v>
+        <v>0.014</v>
       </c>
       <c r="Q243" s="5" t="n">
-        <v>-7.121868</v>
-      </c>
-      <c r="R243" s="5" t="n">
-        <v>-7.121868</v>
+        <v>0.014</v>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -27611,7 +27645,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>May 31, 2024 233,260,909 59,351,182 6,711,620 14,000</t>
+          <t>Share-based payments - - 193,647 -</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -27670,16 +27704,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P244" s="5" t="n">
+        <v>0.193647</v>
       </c>
       <c r="Q244" s="5" t="n">
-        <v>23.918685</v>
-      </c>
-      <c r="R244" s="5" t="n">
-        <v>-42.158117</v>
+        <v>0.193647</v>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -27695,10 +27729,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Private placements 36,507,936 15,000,000 - -</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -27754,18 +27792,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P245" s="5" t="n">
+        <v>-8.499243999999999</v>
       </c>
       <c r="Q245" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.121868</v>
+      </c>
+      <c r="R245" s="5" t="n">
+        <v>-7.121868</v>
       </c>
     </row>
     <row r="246">
@@ -27781,7 +27815,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Return to treasury (19) - - -</t>
+          <t>May 31, 2024 233,260,909 59,351,182 6,711,620 14,000</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -27845,15 +27879,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q246" s="5" t="n">
+        <v>23.918685</v>
+      </c>
+      <c r="R246" s="5" t="n">
+        <v>-42.158117</v>
       </c>
     </row>
     <row r="247">
@@ -27869,7 +27899,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Warrants exercised 28,449,685 9,015,822 (27,313) (14,000)</t>
+          <t>Private placements 36,507,936 15,000,000 - -</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -27934,7 +27964,7 @@
         </is>
       </c>
       <c r="Q247" s="5" t="n">
-        <v>8.974508999999999</v>
+        <v>15</v>
       </c>
       <c r="R247" t="inlineStr">
         <is>
@@ -27955,7 +27985,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Options exercised 4,680,500 2,798,761 (1,224,043) -</t>
+          <t>Return to treasury (19) - - -</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -28019,8 +28049,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q248" s="5" t="n">
-        <v>1.574718</v>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
@@ -28041,7 +28073,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Share issuance costs - (562,559) - -</t>
+          <t>Warrants exercised 28,449,685 9,015,822 (27,313) (14,000)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -28106,7 +28138,7 @@
         </is>
       </c>
       <c r="Q249" s="5" t="n">
-        <v>-0.562559</v>
+        <v>8.974508999999999</v>
       </c>
       <c r="R249" t="inlineStr">
         <is>
@@ -28127,7 +28159,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Share-based payments - - 1,624,031 -</t>
+          <t>Options exercised 4,680,500 2,798,761 (1,224,043) -</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -28192,7 +28224,7 @@
         </is>
       </c>
       <c r="Q250" s="5" t="n">
-        <v>1.624031</v>
+        <v>1.574718</v>
       </c>
       <c r="R250" t="inlineStr">
         <is>
@@ -28213,7 +28245,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>May 31, 2025 302,899,011 $ 85,603,206 $ 7,084,295 $ - $</t>
+          <t>Share issuance costs - (562,559) - -</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -28278,10 +28310,12 @@
         </is>
       </c>
       <c r="Q251" s="5" t="n">
-        <v>36.366793</v>
-      </c>
-      <c r="R251" s="5" t="n">
-        <v>-56.320708</v>
+        <v>-0.562559</v>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -28292,12 +28326,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Accretion expense (notes 5, and 8)</t>
+          <t>Share-based payments - - 1,624,031 -</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -28356,11 +28390,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P252" s="5" t="n">
-        <v>1.132533</v>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q252" s="5" t="n">
-        <v>0.792863</v>
+        <v>1.624031</v>
       </c>
       <c r="R252" t="inlineStr">
         <is>
@@ -28376,19 +28412,15 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Depreciation (note 7)</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>May 31, 2025 302,899,011 $ 85,603,206 $ 7,084,295 $ - $</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -28439,19 +28471,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O253" s="5" t="n">
-        <v>0.006452</v>
-      </c>
-      <c r="P253" s="5" t="n">
-        <v>0.016803</v>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q253" s="5" t="n">
-        <v>0.012889</v>
-      </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>36.366793</v>
+      </c>
+      <c r="R253" s="5" t="n">
+        <v>-56.320708</v>
       </c>
     </row>
     <row r="254">
@@ -28467,14 +28501,10 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) / loss</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Accretion expense (notes 5, and 8)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -28531,10 +28561,10 @@
         </is>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.645938</v>
+        <v>1.132533</v>
       </c>
       <c r="Q254" s="5" t="n">
-        <v>0.031867</v>
+        <v>0.792863</v>
       </c>
       <c r="R254" t="inlineStr">
         <is>
@@ -28555,23 +28585,33 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Geological exploration (note 5)</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Depreciation (note 7)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F255" s="5" t="n">
-        <v>1.050366</v>
-      </c>
-      <c r="G255" s="5" t="n">
-        <v>0.453159</v>
-      </c>
-      <c r="H255" s="5" t="n">
-        <v>0.062928</v>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -28604,13 +28644,13 @@
         </is>
       </c>
       <c r="O255" s="5" t="n">
-        <v>0.273953</v>
+        <v>0.006452</v>
       </c>
       <c r="P255" s="5" t="n">
-        <v>0.680321</v>
+        <v>0.016803</v>
       </c>
       <c r="Q255" s="5" t="n">
-        <v>0.758876</v>
+        <v>0.012889</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
@@ -28631,10 +28671,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Pre-acquisition exploration (notes 6 and 10)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>Foreign exchange (gain) / loss</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -28685,14 +28729,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O256" s="5" t="n">
-        <v>4.262581</v>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P256" s="5" t="n">
-        <v>2.835736</v>
+        <v>0.645938</v>
       </c>
       <c r="Q256" s="5" t="n">
-        <v>2.936359</v>
+        <v>0.031867</v>
       </c>
       <c r="R256" t="inlineStr">
         <is>
@@ -28713,7 +28759,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Impairment to assets held for sale (note 4)</t>
+          <t>Geological exploration (note 5)</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -28722,20 +28768,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F257" s="5" t="n">
+        <v>1.050366</v>
+      </c>
+      <c r="G257" s="5" t="n">
+        <v>0.453159</v>
+      </c>
+      <c r="H257" s="5" t="n">
+        <v>0.062928</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -28767,16 +28807,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O257" s="5" t="n">
+        <v>0.273953</v>
       </c>
       <c r="P257" s="5" t="n">
-        <v>-0.451958</v>
+        <v>0.680321</v>
       </c>
       <c r="Q257" s="5" t="n">
-        <v>-0.189031</v>
+        <v>0.758876</v>
       </c>
       <c r="R257" t="inlineStr">
         <is>
@@ -28797,7 +28835,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Modification of acquisition payable (note 6)</t>
+          <t>Pre-acquisition exploration (notes 6 and 10)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -28851,18 +28889,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O258" s="5" t="n">
+        <v>4.262581</v>
       </c>
       <c r="P258" s="5" t="n">
-        <v>-0.16406</v>
-      </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.835736</v>
+      </c>
+      <c r="Q258" s="5" t="n">
+        <v>2.936359</v>
       </c>
       <c r="R258" t="inlineStr">
         <is>
@@ -28878,12 +28912,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>May 31, 2022 136,716,363 $ 39,125,203 $ 5,942,829 $ - $</t>
+          <t>Impairment to assets held for sale (note 4)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -28943,10 +28977,10 @@
         </is>
       </c>
       <c r="P259" s="5" t="n">
-        <v>18.531027</v>
+        <v>-0.451958</v>
       </c>
       <c r="Q259" s="5" t="n">
-        <v>-26.537005</v>
+        <v>-0.189031</v>
       </c>
       <c r="R259" t="inlineStr">
         <is>
@@ -28962,12 +28996,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Private placements 57,371,133 12,391,930 - -</t>
+          <t>Modification of acquisition payable (note 6)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -29027,7 +29061,7 @@
         </is>
       </c>
       <c r="P260" s="5" t="n">
-        <v>12.39193</v>
+        <v>-0.16406</v>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
@@ -29053,7 +29087,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Shares issued for mineral properties 6,428,570 1,510,714 - -</t>
+          <t>May 31, 2022 136,716,363 $ 39,125,203 $ 5,942,829 $ - $</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -29113,12 +29147,10 @@
         </is>
       </c>
       <c r="P261" s="5" t="n">
-        <v>1.510714</v>
-      </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.531027</v>
+      </c>
+      <c r="Q261" s="5" t="n">
+        <v>-26.537005</v>
       </c>
       <c r="R261" t="inlineStr">
         <is>
@@ -29139,7 +29171,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Warrants exercised 6,463,806 1,174,548 - -</t>
+          <t>Private placements 57,371,133 12,391,930 - -</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -29199,7 +29231,7 @@
         </is>
       </c>
       <c r="P262" s="5" t="n">
-        <v>1.174548</v>
+        <v>12.39193</v>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
@@ -29225,7 +29257,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Shares issued as finders’ fee 303,139 81,204 - -</t>
+          <t>Shares issued for mineral properties 6,428,570 1,510,714 - -</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -29285,7 +29317,7 @@
         </is>
       </c>
       <c r="P263" s="5" t="n">
-        <v>0.081204</v>
+        <v>1.510714</v>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
@@ -29311,7 +29343,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (593,583) - -</t>
+          <t>Warrants exercised 6,463,806 1,174,548 - -</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -29371,7 +29403,7 @@
         </is>
       </c>
       <c r="P264" s="5" t="n">
-        <v>-0.593583</v>
+        <v>1.174548</v>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
@@ -29397,7 +29429,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Share issuance costs – shares - (81,204) - -</t>
+          <t>Shares issued as finders’ fee 303,139 81,204 - -</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -29457,7 +29489,7 @@
         </is>
       </c>
       <c r="P265" s="5" t="n">
-        <v>-0.081204</v>
+        <v>0.081204</v>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
@@ -29483,7 +29515,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ warrants - (18,837) 18,837 -</t>
+          <t>Share issuance costs – cash - (593,583) - -</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -29542,10 +29574,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P266" s="5" t="n">
+        <v>-0.593583</v>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
@@ -29571,7 +29601,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Share-based payments - - 548,686 -</t>
+          <t>Share issuance costs – shares - (81,204) - -</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -29631,7 +29661,7 @@
         </is>
       </c>
       <c r="P267" s="5" t="n">
-        <v>0.548686</v>
+        <v>-0.081204</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
@@ -29657,7 +29687,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>May 31, 2023 207,283,011 53,589,975 6,510,352 -</t>
+          <t>Share issuance costs – finders’ warrants - (18,837) 18,837 -</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -29716,11 +29746,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P268" s="5" t="n">
-        <v>25.064078</v>
-      </c>
-      <c r="Q268" s="5" t="n">
-        <v>-35.036249</v>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
@@ -29741,7 +29775,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>May 31, 2024 233,260,909 $ 59,351,182 $ 6,711,620 $ 14,000 $</t>
+          <t>Share-based payments - - 548,686 -</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -29801,10 +29835,12 @@
         </is>
       </c>
       <c r="P269" s="5" t="n">
-        <v>23.918685</v>
-      </c>
-      <c r="Q269" s="5" t="n">
-        <v>-42.158117</v>
+        <v>0.548686</v>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
@@ -29820,12 +29856,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Accretion expense (notes 6, and 8)</t>
+          <t>May 31, 2023 207,283,011 53,589,975 6,510,352 -</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -29879,16 +29915,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O270" s="5" t="n">
-        <v>1.15573</v>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P270" s="5" t="n">
-        <v>1.132533</v>
-      </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.064078</v>
+      </c>
+      <c r="Q270" s="5" t="n">
+        <v>-35.036249</v>
       </c>
       <c r="R270" t="inlineStr">
         <is>
@@ -29904,63 +29940,75 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares        Amount        Reserves         advance              Deficit              Total</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>May 31, 2024 233,260,909 $ 59,351,182 $ 6,711,620 $ 14,000 $</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F271" s="5" t="n">
-        <v>-0.042631</v>
-      </c>
-      <c r="G271" s="5" t="n">
-        <v>0.02174</v>
-      </c>
-      <c r="H271" s="5" t="n">
-        <v>0.004408</v>
-      </c>
-      <c r="I271" s="5" t="n">
-        <v>0.003206</v>
-      </c>
-      <c r="J271" s="5" t="n">
-        <v>0.00082</v>
-      </c>
-      <c r="K271" s="5" t="n">
-        <v>0.000566</v>
-      </c>
-      <c r="L271" s="5" t="n">
-        <v>0.003911</v>
-      </c>
-      <c r="M271" s="5" t="n">
-        <v>0.02479</v>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O271" s="5" t="n">
-        <v>0.6382679999999999</v>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P271" s="5" t="n">
-        <v>0.645938</v>
-      </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>23.918685</v>
+      </c>
+      <c r="Q271" s="5" t="n">
+        <v>-42.158117</v>
       </c>
       <c r="R271" t="inlineStr">
         <is>
@@ -29981,7 +30029,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Impairment to mineral properties (notes 4 and 5)</t>
+          <t>Accretion expense (notes 6, and 8)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -30035,13 +30083,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O272" s="5" t="n">
+        <v>1.15573</v>
       </c>
       <c r="P272" s="5" t="n">
-        <v>-0.451958</v>
+        <v>1.132533</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -30062,59 +30108,47 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Shares       Amount      Reserves           Deficit            Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>May 31, 2021 135,163,863 $ 38,575,990 $ 5,351,178 $</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F273" s="5" t="n">
+        <v>-0.042631</v>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>0.02174</v>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>0.004408</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>0.003206</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>0.000566</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>0.003911</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>0.02479</v>
       </c>
       <c r="N273" t="inlineStr">
         <is>
@@ -30122,10 +30156,10 @@
         </is>
       </c>
       <c r="O273" s="5" t="n">
-        <v>26.161224</v>
+        <v>0.6382679999999999</v>
       </c>
       <c r="P273" s="5" t="n">
-        <v>-17.765944</v>
+        <v>0.645938</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -30146,12 +30180,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Shares       Amount      Reserves           Deficit            Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Warrant exercised 802,500 96,300 -</t>
+          <t>Impairment to mineral properties (notes 4 and 5)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -30205,13 +30239,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O274" s="5" t="n">
-        <v>0.0963</v>
-      </c>
-      <c r="P274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P274" s="5" t="n">
+        <v>-0.451958</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -30237,7 +30271,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Option exercised 750,000 452,913 (201,663)</t>
+          <t>May 31, 2021 135,163,863 $ 38,575,990 $ 5,351,178 $</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -30292,12 +30326,10 @@
         </is>
       </c>
       <c r="O275" s="5" t="n">
-        <v>0.25125</v>
-      </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>26.161224</v>
+      </c>
+      <c r="P275" s="5" t="n">
+        <v>-17.765944</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -30323,7 +30355,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Share-based payments - - 793,314</t>
+          <t>Warrant exercised 802,500 96,300 -</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -30378,7 +30410,7 @@
         </is>
       </c>
       <c r="O276" s="5" t="n">
-        <v>0.793314</v>
+        <v>0.0963</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -30409,14 +30441,10 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Option exercised 750,000 452,913 (201,663)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -30468,10 +30496,12 @@
         </is>
       </c>
       <c r="O277" s="5" t="n">
-        <v>-8.771061</v>
-      </c>
-      <c r="P277" s="5" t="n">
-        <v>-8.771061</v>
+        <v>0.25125</v>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -30497,7 +30527,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>May 31, 2022 136,716,363 39,125,203 5,942,829</t>
+          <t>Share-based payments - - 793,314</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -30552,10 +30582,12 @@
         </is>
       </c>
       <c r="O278" s="5" t="n">
-        <v>18.531027</v>
-      </c>
-      <c r="P278" s="5" t="n">
-        <v>-26.537005</v>
+        <v>0.793314</v>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -30581,10 +30613,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Private Placements 57,371,133 12,391,930 -</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -30636,12 +30672,10 @@
         </is>
       </c>
       <c r="O279" s="5" t="n">
-        <v>12.39193</v>
-      </c>
-      <c r="P279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.771061</v>
+      </c>
+      <c r="P279" s="5" t="n">
+        <v>-8.771061</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -30667,7 +30701,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Shares issued for mineral properties (note 5) 6,428,570 1,510,714 -</t>
+          <t>May 31, 2022 136,716,363 39,125,203 5,942,829</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -30722,12 +30756,10 @@
         </is>
       </c>
       <c r="O280" s="5" t="n">
-        <v>1.510714</v>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.531027</v>
+      </c>
+      <c r="P280" s="5" t="n">
+        <v>-26.537005</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -30753,7 +30785,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Warrants exercised 6,463,806 1,174,548 -</t>
+          <t>Private Placements 57,371,133 12,391,930 -</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -30808,7 +30840,7 @@
         </is>
       </c>
       <c r="O281" s="5" t="n">
-        <v>1.174548</v>
+        <v>12.39193</v>
       </c>
       <c r="P281" t="inlineStr">
         <is>
@@ -30839,7 +30871,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Shares issued as finders’ fees 303,139 81,204 -</t>
+          <t>Shares issued for mineral properties (note 5) 6,428,570 1,510,714 -</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -30894,7 +30926,7 @@
         </is>
       </c>
       <c r="O282" s="5" t="n">
-        <v>0.081204</v>
+        <v>1.510714</v>
       </c>
       <c r="P282" t="inlineStr">
         <is>
@@ -30925,7 +30957,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (593,583) -</t>
+          <t>Warrants exercised 6,463,806 1,174,548 -</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -30980,7 +31012,7 @@
         </is>
       </c>
       <c r="O283" s="5" t="n">
-        <v>-0.593583</v>
+        <v>1.174548</v>
       </c>
       <c r="P283" t="inlineStr">
         <is>
@@ -31011,7 +31043,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Share issuance costs – shares - (81,204) -</t>
+          <t>Shares issued as finders’ fees 303,139 81,204 -</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -31066,7 +31098,7 @@
         </is>
       </c>
       <c r="O284" s="5" t="n">
-        <v>-0.081204</v>
+        <v>0.081204</v>
       </c>
       <c r="P284" t="inlineStr">
         <is>
@@ -31097,7 +31129,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ warrants - (18,837) 18,837</t>
+          <t>Share issuance costs – cash - (593,583) -</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -31151,10 +31183,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O285" s="5" t="n">
+        <v>-0.593583</v>
       </c>
       <c r="P285" t="inlineStr">
         <is>
@@ -31185,7 +31215,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Share-based payments - - 548,686</t>
+          <t>Share issuance costs – shares - (81,204) -</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -31240,7 +31270,7 @@
         </is>
       </c>
       <c r="O286" s="5" t="n">
-        <v>0.548686</v>
+        <v>-0.081204</v>
       </c>
       <c r="P286" t="inlineStr">
         <is>
@@ -31271,7 +31301,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>May 31, 2023 207,283,011 $ 53,589,975 $ 6,510,352 $</t>
+          <t>Share issuance costs – finders’ warrants - (18,837) 18,837</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -31325,11 +31355,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O287" s="5" t="n">
-        <v>25.064078</v>
-      </c>
-      <c r="P287" s="5" t="n">
-        <v>-35.036249</v>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -31350,12 +31384,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares       Amount      Reserves           Deficit            Total</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Accounting and legal (note 9) $</t>
+          <t>Share-based payments - - 548,686</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -31404,11 +31438,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N288" s="5" t="n">
-        <v>0.232552</v>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O288" s="5" t="n">
-        <v>0.172886</v>
+        <v>0.548686</v>
       </c>
       <c r="P288" t="inlineStr">
         <is>
@@ -31434,12 +31470,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares       Amount      Reserves           Deficit            Total</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Accretion expense (notes 5, 6, and 7)</t>
+          <t>May 31, 2023 207,283,011 $ 53,589,975 $ 6,510,352 $</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -31488,16 +31524,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N289" s="5" t="n">
-        <v>0.641232</v>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O289" s="5" t="n">
-        <v>1.15573</v>
-      </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.064078</v>
+      </c>
+      <c r="P289" s="5" t="n">
+        <v>-35.036249</v>
       </c>
       <c r="Q289" t="inlineStr">
         <is>
@@ -31523,14 +31559,10 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Consulting fees (note 9)</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounting and legal (note 9) $</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -31577,10 +31609,10 @@
         </is>
       </c>
       <c r="N290" s="5" t="n">
-        <v>0.813283</v>
+        <v>0.232552</v>
       </c>
       <c r="O290" s="5" t="n">
-        <v>0.328244</v>
+        <v>0.172886</v>
       </c>
       <c r="P290" t="inlineStr">
         <is>
@@ -31611,7 +31643,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Corporate secretarial (note 9)</t>
+          <t>Accretion expense (notes 5, 6, and 7)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -31661,10 +31693,10 @@
         </is>
       </c>
       <c r="N291" s="5" t="n">
-        <v>0.03075</v>
+        <v>0.641232</v>
       </c>
       <c r="O291" s="5" t="n">
-        <v>0.033</v>
+        <v>1.15573</v>
       </c>
       <c r="P291" t="inlineStr">
         <is>
@@ -31695,12 +31727,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Depreciation (note 6)</t>
+          <t>Consulting fees (note 9)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -31748,13 +31780,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N292" s="5" t="n">
+        <v>0.813283</v>
       </c>
       <c r="O292" s="5" t="n">
-        <v>0.006452</v>
+        <v>0.328244</v>
       </c>
       <c r="P292" t="inlineStr">
         <is>
@@ -31785,7 +31815,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Directors’ fees (note 9)</t>
+          <t>Corporate secretarial (note 9)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -31835,10 +31865,10 @@
         </is>
       </c>
       <c r="N293" s="5" t="n">
-        <v>0.05</v>
+        <v>0.03075</v>
       </c>
       <c r="O293" s="5" t="n">
-        <v>0.08875</v>
+        <v>0.033</v>
       </c>
       <c r="P293" t="inlineStr">
         <is>
@@ -31869,10 +31899,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Foreign exchange (recovery)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Depreciation (note 6)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -31913,14 +31947,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M294" s="5" t="n">
-        <v>0.02479</v>
-      </c>
-      <c r="N294" s="5" t="n">
-        <v>-0.772412</v>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O294" s="5" t="n">
-        <v>0.6382679999999999</v>
+        <v>0.006452</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -31951,10 +31989,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Geological exploration (note 4)</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Directors’ fees (note 9)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -31995,14 +32037,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M295" s="5" t="n">
-        <v>0.328885</v>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N295" s="5" t="n">
-        <v>0.299405</v>
+        <v>0.05</v>
       </c>
       <c r="O295" s="5" t="n">
-        <v>0.273953</v>
+        <v>0.08875</v>
       </c>
       <c r="P295" t="inlineStr">
         <is>
@@ -32033,7 +32077,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Office and sundry (note 9)</t>
+          <t>Foreign exchange (recovery)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -32077,16 +32121,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M296" s="5" t="n">
+        <v>0.02479</v>
       </c>
       <c r="N296" s="5" t="n">
-        <v>0.092303</v>
+        <v>-0.772412</v>
       </c>
       <c r="O296" s="5" t="n">
-        <v>0.125052</v>
+        <v>0.6382679999999999</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -32117,7 +32159,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Pre-acquisition exploration (note 5)</t>
+          <t>Geological exploration (note 4)</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -32162,13 +32204,13 @@
         </is>
       </c>
       <c r="M297" s="5" t="n">
-        <v>0.280769</v>
+        <v>0.328885</v>
       </c>
       <c r="N297" s="5" t="n">
-        <v>1.351483</v>
+        <v>0.299405</v>
       </c>
       <c r="O297" s="5" t="n">
-        <v>4.262581</v>
+        <v>0.273953</v>
       </c>
       <c r="P297" t="inlineStr">
         <is>
@@ -32199,7 +32241,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Share-based payments (notes 8 and 9)</t>
+          <t>Office and sundry (note 9)</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -32249,10 +32291,10 @@
         </is>
       </c>
       <c r="N298" s="5" t="n">
-        <v>3.506331</v>
+        <v>0.092303</v>
       </c>
       <c r="O298" s="5" t="n">
-        <v>0.793314</v>
+        <v>0.125052</v>
       </c>
       <c r="P298" t="inlineStr">
         <is>
@@ -32283,7 +32325,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Wages and salaries (note 9)</t>
+          <t>Pre-acquisition exploration (note 5)</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -32327,16 +32369,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M299" s="5" t="n">
+        <v>0.280769</v>
       </c>
       <c r="N299" s="5" t="n">
-        <v>0.085615</v>
+        <v>1.351483</v>
       </c>
       <c r="O299" s="5" t="n">
-        <v>0.248624</v>
+        <v>4.262581</v>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -32367,7 +32407,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable (note 10)</t>
+          <t>Share-based payments (notes 8 and 9)</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -32417,12 +32457,10 @@
         </is>
       </c>
       <c r="N300" s="5" t="n">
-        <v>0.12304</v>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.506331</v>
+      </c>
+      <c r="O300" s="5" t="n">
+        <v>0.793314</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
@@ -32453,19 +32491,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E301" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="F301" s="5" t="n">
-        <v>30.03619</v>
+          <t>Wages and salaries (note 9)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -32503,10 +32541,10 @@
         </is>
       </c>
       <c r="N301" s="5" t="n">
-        <v>120.365569</v>
+        <v>0.085615</v>
       </c>
       <c r="O301" s="5" t="n">
-        <v>135.814199</v>
+        <v>0.248624</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
@@ -32532,12 +32570,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Shares         Amount         Reserves              Deficit              Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>May 31, 2020 91,179,419 $ 14,657,966 $ 2,040,235 $</t>
+          <t>Gain on settlement of accounts payable (note 10)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -32587,10 +32625,12 @@
         </is>
       </c>
       <c r="N302" s="5" t="n">
-        <v>5.831465</v>
-      </c>
-      <c r="O302" s="5" t="n">
-        <v>-10.866736</v>
+        <v>0.12304</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
@@ -32616,24 +32656,24 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Shares         Amount         Reserves              Deficit              Total</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Private placement shares issued 26,362,442 17,135,588 -</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>30.03619</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -32671,12 +32711,10 @@
         </is>
       </c>
       <c r="N303" s="5" t="n">
-        <v>17.135588</v>
-      </c>
-      <c r="O303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>120.365569</v>
+      </c>
+      <c r="O303" s="5" t="n">
+        <v>135.814199</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -32707,7 +32745,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Finders share issued 290,360 188,734 -</t>
+          <t>May 31, 2020 91,179,419 $ 14,657,966 $ 2,040,235 $</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -32757,12 +32795,10 @@
         </is>
       </c>
       <c r="N304" s="5" t="n">
-        <v>0.188734</v>
-      </c>
-      <c r="O304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.831465</v>
+      </c>
+      <c r="O304" s="5" t="n">
+        <v>-10.866736</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
@@ -32793,7 +32829,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Warrant exercised 10,306,020 1,526,037 (90,909)</t>
+          <t>Private placement shares issued 26,362,442 17,135,588 -</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -32843,7 +32879,7 @@
         </is>
       </c>
       <c r="N305" s="5" t="n">
-        <v>1.435128</v>
+        <v>17.135588</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -32879,7 +32915,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Stock options exercised 337,500 234,979</t>
+          <t>Finders share issued 290,360 188,734 -</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -32929,10 +32965,12 @@
         </is>
       </c>
       <c r="N306" s="5" t="n">
-        <v>0.1305</v>
-      </c>
-      <c r="O306" s="5" t="n">
-        <v>-0.104479</v>
+        <v>0.188734</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -32963,7 +33001,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (821,201) -</t>
+          <t>Warrant exercised 10,306,020 1,526,037 (90,909)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -33013,7 +33051,7 @@
         </is>
       </c>
       <c r="N307" s="5" t="n">
-        <v>-0.821201</v>
+        <v>1.435128</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -33049,7 +33087,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ shares - (188,734) -</t>
+          <t>Stock options exercised 337,500 234,979</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -33099,12 +33137,10 @@
         </is>
       </c>
       <c r="N308" s="5" t="n">
-        <v>-0.188734</v>
-      </c>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1305</v>
+      </c>
+      <c r="O308" s="5" t="n">
+        <v>-0.104479</v>
       </c>
       <c r="P308" t="inlineStr">
         <is>
@@ -33135,7 +33171,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Shares issued for deferred acquisition costs 6,688,122 5,842,621 -</t>
+          <t>Share issuance costs – cash - (821,201) -</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -33185,7 +33221,7 @@
         </is>
       </c>
       <c r="N309" s="5" t="n">
-        <v>5.842621</v>
+        <v>-0.821201</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -33221,7 +33257,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Share-based payments - - 3,506,331</t>
+          <t>Share issuance costs – finders’ shares - (188,734) -</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -33271,7 +33307,7 @@
         </is>
       </c>
       <c r="N310" s="5" t="n">
-        <v>3.506331</v>
+        <v>-0.188734</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -33307,14 +33343,10 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued for deferred acquisition costs 6,688,122 5,842,621 -</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -33361,10 +33393,12 @@
         </is>
       </c>
       <c r="N311" s="5" t="n">
-        <v>-6.899208</v>
-      </c>
-      <c r="O311" s="5" t="n">
-        <v>-6.899208</v>
+        <v>5.842621</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
@@ -33395,7 +33429,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>May 31, 2021 135,163,863 38,575,990 5,351,178</t>
+          <t>Share-based payments - - 3,506,331</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -33445,10 +33479,12 @@
         </is>
       </c>
       <c r="N312" s="5" t="n">
-        <v>26.161224</v>
-      </c>
-      <c r="O312" s="5" t="n">
-        <v>-17.765944</v>
+        <v>3.506331</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
@@ -33479,10 +33515,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Warrants exercised 802,500 96,300 -</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -33529,12 +33569,10 @@
         </is>
       </c>
       <c r="N313" s="5" t="n">
-        <v>0.0963</v>
-      </c>
-      <c r="O313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.899208</v>
+      </c>
+      <c r="O313" s="5" t="n">
+        <v>-6.899208</v>
       </c>
       <c r="P313" t="inlineStr">
         <is>
@@ -33565,7 +33603,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Options exercised 750,000 452,913 (201,663)</t>
+          <t>May 31, 2021 135,163,863 38,575,990 5,351,178</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -33615,12 +33653,10 @@
         </is>
       </c>
       <c r="N314" s="5" t="n">
-        <v>0.25125</v>
-      </c>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>26.161224</v>
+      </c>
+      <c r="O314" s="5" t="n">
+        <v>-17.765944</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
@@ -33651,7 +33687,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Share-based payments - - 793,314</t>
+          <t>Warrants exercised 802,500 96,300 -</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -33701,7 +33737,7 @@
         </is>
       </c>
       <c r="N315" s="5" t="n">
-        <v>0.793314</v>
+        <v>0.0963</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -33737,7 +33773,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>May 31, 2022 136,716,363 $ 39,125,203 $ 5,942,829 $</t>
+          <t>Options exercised 750,000 452,913 (201,663)</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -33787,10 +33823,12 @@
         </is>
       </c>
       <c r="N316" s="5" t="n">
-        <v>18.531027</v>
-      </c>
-      <c r="O316" s="5" t="n">
-        <v>-26.537005</v>
+        <v>0.25125</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
@@ -33816,12 +33854,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares         Amount         Reserves              Deficit              Total</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Accounting and legal (note 8) $</t>
+          <t>Share-based payments - - 793,314</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -33860,14 +33898,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L317" s="5" t="n">
-        <v>0.073043</v>
-      </c>
-      <c r="M317" s="5" t="n">
-        <v>0.179995</v>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N317" s="5" t="n">
-        <v>0.232552</v>
+        <v>0.793314</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -33898,12 +33940,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares         Amount         Reserves              Deficit              Total</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Accretion expense (notes 4, 5, and 6)</t>
+          <t>May 31, 2022 136,716,363 $ 39,125,203 $ 5,942,829 $</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -33947,16 +33989,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M318" s="5" t="n">
-        <v>0.062136</v>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N318" s="5" t="n">
-        <v>0.641232</v>
-      </c>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.531027</v>
+      </c>
+      <c r="O318" s="5" t="n">
+        <v>-26.537005</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -33987,14 +34029,10 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Consulting fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounting and legal (note 8) $</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -34031,13 +34069,13 @@
         </is>
       </c>
       <c r="L319" s="5" t="n">
-        <v>0.18</v>
+        <v>0.073043</v>
       </c>
       <c r="M319" s="5" t="n">
-        <v>0.280504</v>
+        <v>0.179995</v>
       </c>
       <c r="N319" s="5" t="n">
-        <v>0.813283</v>
+        <v>0.232552</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -34073,7 +34111,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Corporate secretarial (note 8)</t>
+          <t>Accretion expense (notes 4, 5, and 6)</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -34112,14 +34150,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L320" s="5" t="n">
-        <v>0.015</v>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.02325</v>
+        <v>0.062136</v>
       </c>
       <c r="N320" s="5" t="n">
-        <v>0.03075</v>
+        <v>0.641232</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -34155,10 +34195,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Directors’ fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
+          <t>Consulting fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -34195,13 +34239,13 @@
         </is>
       </c>
       <c r="L321" s="5" t="n">
-        <v>0.027</v>
+        <v>0.18</v>
       </c>
       <c r="M321" s="5" t="n">
-        <v>0.036</v>
+        <v>0.280504</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>0.05</v>
+        <v>0.813283</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -34237,7 +34281,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Office and sundry (note 8)</t>
+          <t>Corporate secretarial (note 8)</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -34277,13 +34321,13 @@
         </is>
       </c>
       <c r="L322" s="5" t="n">
-        <v>0.100201</v>
+        <v>0.015</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>0.109492</v>
+        <v>0.02325</v>
       </c>
       <c r="N322" s="5" t="n">
-        <v>0.092303</v>
+        <v>0.03075</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -34319,10 +34363,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Share-based payments (notes 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
+          <t>Directors’ fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -34358,16 +34406,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L323" s="5" t="n">
+        <v>0.027</v>
       </c>
       <c r="M323" s="5" t="n">
-        <v>1.256182</v>
+        <v>0.036</v>
       </c>
       <c r="N323" s="5" t="n">
-        <v>3.506331</v>
+        <v>0.05</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -34403,7 +34449,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Wages and salaries (note 8)</t>
+          <t>Office and sundry (note 8)</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -34442,18 +34488,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L324" s="5" t="n">
+        <v>0.100201</v>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>0.109492</v>
       </c>
       <c r="N324" s="5" t="n">
-        <v>0.085615</v>
+        <v>0.092303</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -34489,7 +34531,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable (note 9)</t>
+          <t>Share-based payments (notes 7 and 8)</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -34534,10 +34576,10 @@
         </is>
       </c>
       <c r="M325" s="5" t="n">
-        <v>0.160092</v>
+        <v>1.256182</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>0.12304</v>
+        <v>3.506331</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -34573,7 +34615,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Gain on settlement of convertible notes (note 6)</t>
+          <t>Wages and salaries (note 8)</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -34617,13 +34659,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M326" s="5" t="n">
-        <v>0.186929</v>
-      </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N326" s="5" t="n">
+        <v>0.085615</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -34659,14 +34701,10 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Loss before income tax</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable (note 9)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -34702,14 +34740,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L327" s="5" t="n">
-        <v>-0.570663</v>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M327" s="5" t="n">
-        <v>-3.08078</v>
+        <v>0.160092</v>
       </c>
       <c r="N327" s="5" t="n">
-        <v>-6.899208</v>
+        <v>0.12304</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -34745,7 +34785,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (note 10)</t>
+          <t>Gain on settlement of convertible notes (note 6)</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -34790,7 +34830,7 @@
         </is>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.040306</v>
+        <v>0.186929</v>
       </c>
       <c r="N328" t="inlineStr">
         <is>
@@ -34826,15 +34866,19 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Loss attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Owners of the parent</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>Loss before income tax</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -34874,7 +34918,7 @@
         <v>-0.570663</v>
       </c>
       <c r="M329" s="5" t="n">
-        <v>-3.020381</v>
+        <v>-3.08078</v>
       </c>
       <c r="N329" s="5" t="n">
         <v>-6.899208</v>
@@ -34908,17 +34952,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Loss attributable to</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Deferred income tax recovery (note 10)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -34962,7 +35006,7 @@
         </is>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.020093</v>
+        <v>0.040306</v>
       </c>
       <c r="N330" t="inlineStr">
         <is>
@@ -35003,7 +35047,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Loss attributable to total</t>
+          <t>Owners of the parent</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -35046,7 +35090,7 @@
         <v>-0.570663</v>
       </c>
       <c r="M331" s="5" t="n">
-        <v>-3.040474</v>
+        <v>-3.020381</v>
       </c>
       <c r="N331" s="5" t="n">
         <v>-6.899208</v>
@@ -35085,12 +35129,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Non-controlling interest</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>MinorityInterests</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -35128,14 +35172,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L332" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M332" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="N332" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.020093</v>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -35171,14 +35219,10 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Loss attributable to total</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -35215,13 +35259,13 @@
         </is>
       </c>
       <c r="L333" s="5" t="n">
-        <v>27.787384</v>
+        <v>-0.570663</v>
       </c>
       <c r="M333" s="5" t="n">
-        <v>56.889871</v>
+        <v>-3.040474</v>
       </c>
       <c r="N333" s="5" t="n">
-        <v>120.365569</v>
+        <v>-6.899208</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -35252,15 +35296,19 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>received in                          convertible                                              controlling       Total equity</t>
+          <t>Loss attributable to</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>May 31, 2019 27,787,371 $ 6,495,478 $ 89,040 $ 708,430 $ - $ (7,846,355) $ (553,407) $</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -35296,18 +35344,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L334" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>-0.553407</v>
-      </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="N334" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -35338,15 +35382,19 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>received in                          convertible                                              controlling       Total equity</t>
+          <t>Loss attributable to</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Private placement shares issued 55,985,462 7,358,837 (89,040) - - - 7,269,797</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -35382,18 +35430,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L335" s="5" t="n">
+        <v>27.787384</v>
       </c>
       <c r="M335" s="5" t="n">
-        <v>7.269797</v>
-      </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>56.889871</v>
+      </c>
+      <c r="N335" s="5" t="n">
+        <v>120.365569</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -35429,7 +35473,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Finders’ share issued 1,041,586 208,317 - - - - 208,317</t>
+          <t>May 31, 2019 27,787,371 $ 6,495,478 $ 89,040 $ 708,430 $ - $ (7,846,355) $ (553,407) $</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -35474,7 +35518,7 @@
         </is>
       </c>
       <c r="M336" s="5" t="n">
-        <v>0.208317</v>
+        <v>-0.553407</v>
       </c>
       <c r="N336" t="inlineStr">
         <is>
@@ -35515,7 +35559,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Warrant exercised 2,365,000 283,800</t>
+          <t>Private placement shares issued 55,985,462 7,358,837 (89,040) - - - 7,269,797</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -35560,10 +35604,12 @@
         </is>
       </c>
       <c r="M337" s="5" t="n">
-        <v>0.2838</v>
-      </c>
-      <c r="N337" s="5" t="n">
-        <v>0.2838</v>
+        <v>7.269797</v>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
@@ -35599,7 +35645,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Share issuance costs – cash - (189,240) - - - - (189,240)</t>
+          <t>Finders’ share issued 1,041,586 208,317 - - - - 208,317</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -35644,7 +35690,7 @@
         </is>
       </c>
       <c r="M338" s="5" t="n">
-        <v>-0.18924</v>
+        <v>0.208317</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
@@ -35685,7 +35731,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ shares - (208,317)</t>
+          <t>Warrant exercised 2,365,000 283,800</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -35730,10 +35776,10 @@
         </is>
       </c>
       <c r="M339" s="5" t="n">
-        <v>-0.208317</v>
+        <v>0.2838</v>
       </c>
       <c r="N339" s="5" t="n">
-        <v>-0.208317</v>
+        <v>0.2838</v>
       </c>
       <c r="O339" t="inlineStr">
         <is>
@@ -35769,7 +35815,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ warrants - (90,909) - 90,909 - - -</t>
+          <t>Share issuance costs – cash - (189,240) - - - - (189,240)</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -35813,10 +35859,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M340" s="5" t="n">
+        <v>-0.18924</v>
       </c>
       <c r="N340" t="inlineStr">
         <is>
@@ -35857,7 +35901,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal (note 4) - - - - - - -</t>
+          <t>Share issuance costs – finders’ shares - (208,317)</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -35902,10 +35946,10 @@
         </is>
       </c>
       <c r="M341" s="5" t="n">
-        <v>0.443168</v>
+        <v>-0.208317</v>
       </c>
       <c r="N341" s="5" t="n">
-        <v>0.443168</v>
+        <v>-0.208317</v>
       </c>
       <c r="O341" t="inlineStr">
         <is>
@@ -35936,12 +35980,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal non-</t>
+          <t>received in                          convertible                                              controlling       Total equity</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal non- controlling interest (note 4) - - - (124,260) - - (124,260)</t>
+          <t>Share issuance costs – finders’ warrants - (90,909) - 90,909 - - -</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -35980,14 +36024,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L342" s="5" t="n">
-        <v>-0.547335</v>
-      </c>
-      <c r="M342" s="5" t="n">
-        <v>-0.547335</v>
-      </c>
-      <c r="N342" s="5" t="n">
-        <v>-0.423075</v>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
@@ -36018,12 +36068,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal non-</t>
+          <t>received in                          convertible                                              controlling       Total equity</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Issuance of convertible debt - - - - 149,280 - 149,280</t>
+          <t>Acquisition of Minera Cachinal (note 4) - - - - - - -</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -36068,12 +36118,10 @@
         </is>
       </c>
       <c r="M343" s="5" t="n">
-        <v>0.14928</v>
-      </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.443168</v>
+      </c>
+      <c r="N343" s="5" t="n">
+        <v>0.443168</v>
       </c>
       <c r="O343" t="inlineStr">
         <is>
@@ -36109,7 +36157,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Deferred tax on equity conversion feature - - - - (40,306) - (40,306)</t>
+          <t>Acquisition of Minera Cachinal non- controlling interest (note 4) - - - (124,260) - - (124,260)</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -36149,15 +36197,13 @@
         </is>
       </c>
       <c r="L344" s="5" t="n">
-        <v>-0.040306</v>
+        <v>-0.547335</v>
       </c>
       <c r="M344" s="5" t="n">
-        <v>-0.040306</v>
-      </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.547335</v>
+      </c>
+      <c r="N344" s="5" t="n">
+        <v>-0.423075</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -36193,7 +36239,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Settlement of convertible note (net) 4,000,000 800,000 - 108,974 (108,974) 800,000</t>
+          <t>Issuance of convertible debt - - - - 149,280 - 149,280</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -36238,7 +36284,7 @@
         </is>
       </c>
       <c r="M345" s="5" t="n">
-        <v>0.8</v>
+        <v>0.14928</v>
       </c>
       <c r="N345" t="inlineStr">
         <is>
@@ -36279,7 +36325,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Share-based payments - - - 1,256,182 - 1,256,182</t>
+          <t>Deferred tax on equity conversion feature - - - - (40,306) - (40,306)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -36318,13 +36364,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L346" s="5" t="n">
+        <v>-0.040306</v>
       </c>
       <c r="M346" s="5" t="n">
-        <v>1.256182</v>
+        <v>-0.040306</v>
       </c>
       <c r="N346" t="inlineStr">
         <is>
@@ -36365,7 +36409,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - - (3,020,381) (3,020,381)</t>
+          <t>Settlement of convertible note (net) 4,000,000 800,000 - 108,974 (108,974) 800,000</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -36404,14 +36448,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L347" s="5" t="n">
-        <v>-3.040474</v>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M347" s="5" t="n">
-        <v>-3.040474</v>
-      </c>
-      <c r="N347" s="5" t="n">
-        <v>-0.020093</v>
+        <v>0.8</v>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -36447,7 +36495,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>May 31, 2020 91,179,419 14,657,966 - 2,040,235 - (10,866,736) 5,831,465</t>
+          <t>Share-based payments - - - 1,256,182 - 1,256,182</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -36492,7 +36540,7 @@
         </is>
       </c>
       <c r="M348" s="5" t="n">
-        <v>5.831465</v>
+        <v>1.256182</v>
       </c>
       <c r="N348" t="inlineStr">
         <is>
@@ -36533,7 +36581,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Private placement shares issued 26,362,442 17,135,588 - - - - 17,135,588</t>
+          <t>Loss for the year - - - - - (3,020,381) (3,020,381)</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -36572,18 +36620,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L349" s="5" t="n">
+        <v>-3.040474</v>
       </c>
       <c r="M349" s="5" t="n">
-        <v>17.135588</v>
-      </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.040474</v>
+      </c>
+      <c r="N349" s="5" t="n">
+        <v>-0.020093</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -36619,7 +36663,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Finders’ share issued 290,360 188,734 - - - - 188,734</t>
+          <t>May 31, 2020 91,179,419 14,657,966 - 2,040,235 - (10,866,736) 5,831,465</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -36664,7 +36708,7 @@
         </is>
       </c>
       <c r="M350" s="5" t="n">
-        <v>0.188734</v>
+        <v>5.831465</v>
       </c>
       <c r="N350" t="inlineStr">
         <is>
@@ -36705,7 +36749,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Warrants exercised 10,306,020 1,526,037 - (90,909) - - 1,435,128</t>
+          <t>Private placement shares issued 26,362,442 17,135,588 - - - - 17,135,588</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -36750,7 +36794,7 @@
         </is>
       </c>
       <c r="M351" s="5" t="n">
-        <v>1.435128</v>
+        <v>17.135588</v>
       </c>
       <c r="N351" t="inlineStr">
         <is>
@@ -36791,7 +36835,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Stock options exercised 337,500 234,979 - (104,479) - - 130,500</t>
+          <t>Finders’ share issued 290,360 188,734 - - - - 188,734</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -36836,7 +36880,7 @@
         </is>
       </c>
       <c r="M352" s="5" t="n">
-        <v>0.1305</v>
+        <v>0.188734</v>
       </c>
       <c r="N352" t="inlineStr">
         <is>
@@ -36877,7 +36921,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (821,201) - - - - (821,201)</t>
+          <t>Warrants exercised 10,306,020 1,526,037 - (90,909) - - 1,435,128</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -36922,7 +36966,7 @@
         </is>
       </c>
       <c r="M353" s="5" t="n">
-        <v>-0.821201</v>
+        <v>1.435128</v>
       </c>
       <c r="N353" t="inlineStr">
         <is>
@@ -36963,7 +37007,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ shares - (188,734) - - - -</t>
+          <t>Stock options exercised 337,500 234,979 - (104,479) - - 130,500</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -37008,10 +37052,12 @@
         </is>
       </c>
       <c r="M354" s="5" t="n">
-        <v>-0.188734</v>
-      </c>
-      <c r="N354" s="5" t="n">
-        <v>-0.188734</v>
+        <v>0.1305</v>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -37047,7 +37093,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Shares issued for deferred acquisition costs 6,688,122 5,842,621 - - - - 5,842,621</t>
+          <t>Share issuance costs - cash - (821,201) - - - - (821,201)</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -37092,7 +37138,7 @@
         </is>
       </c>
       <c r="M355" s="5" t="n">
-        <v>5.842621</v>
+        <v>-0.821201</v>
       </c>
       <c r="N355" t="inlineStr">
         <is>
@@ -37133,7 +37179,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Share-based payments - - - 3,506,331 - - 3,506,331</t>
+          <t>Share issuance costs – finders’ shares - (188,734) - - - -</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -37178,12 +37224,10 @@
         </is>
       </c>
       <c r="M356" s="5" t="n">
-        <v>3.506331</v>
-      </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.188734</v>
+      </c>
+      <c r="N356" s="5" t="n">
+        <v>-0.188734</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -37219,7 +37263,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - - (6,899,208) (6,899,208)</t>
+          <t>Shares issued for deferred acquisition costs 6,688,122 5,842,621 - - - - 5,842,621</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -37264,7 +37308,7 @@
         </is>
       </c>
       <c r="M357" s="5" t="n">
-        <v>-6.899208</v>
+        <v>5.842621</v>
       </c>
       <c r="N357" t="inlineStr">
         <is>
@@ -37305,7 +37349,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>May 31, 2021 135,163,863 $ 38,575,990 $ - $ 5,351,178 $ - $ (17,765,944) $ 26,161,224 $</t>
+          <t>Share-based payments - - - 3,506,331 - - 3,506,331</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -37350,7 +37394,7 @@
         </is>
       </c>
       <c r="M358" s="5" t="n">
-        <v>26.161224</v>
+        <v>3.506331</v>
       </c>
       <c r="N358" t="inlineStr">
         <is>
@@ -37386,12 +37430,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Acquisition of Minera Cachinal non-</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Accretion expense (notes 4 and 6)</t>
+          <t>Loss for the year - - - - - (6,899,208) (6,899,208)</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -37436,7 +37480,7 @@
         </is>
       </c>
       <c r="M359" s="5" t="n">
-        <v>0.062136</v>
+        <v>-6.899208</v>
       </c>
       <c r="N359" t="inlineStr">
         <is>
@@ -37472,12 +37516,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Acquisition of Minera Cachinal non-</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Property investigation (notes 4 and 5)</t>
+          <t>May 31, 2021 135,163,863 $ 38,575,990 $ - $ 5,351,178 $ - $ (17,765,944) $ 26,161,224 $</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -37516,11 +37560,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L360" s="5" t="n">
-        <v>0.051547</v>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M360" s="5" t="n">
-        <v>0.280769</v>
+        <v>26.161224</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>
@@ -37561,7 +37607,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>Accretion expense (notes 4 and 6)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -37606,7 +37652,7 @@
         </is>
       </c>
       <c r="M361" s="5" t="n">
-        <v>0.160092</v>
+        <v>0.062136</v>
       </c>
       <c r="N361" t="inlineStr">
         <is>
@@ -37647,7 +37693,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Gain on settlement of convertible note (note 6)</t>
+          <t>Property investigation (notes 4 and 5)</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -37686,13 +37732,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L362" s="5" t="n">
+        <v>0.051547</v>
       </c>
       <c r="M362" s="5" t="n">
-        <v>0.186929</v>
+        <v>0.280769</v>
       </c>
       <c r="N362" t="inlineStr">
         <is>
@@ -37733,7 +37777,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery (notes 6 and 10)</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -37778,7 +37822,7 @@
         </is>
       </c>
       <c r="M363" s="5" t="n">
-        <v>0.040306</v>
+        <v>0.160092</v>
       </c>
       <c r="N363" t="inlineStr">
         <is>
@@ -37819,14 +37863,10 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of convertible note (note 6)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -37862,11 +37902,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L364" s="5" t="n">
-        <v>-0.570663</v>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M364" s="5" t="n">
-        <v>-3.040474</v>
+        <v>0.186929</v>
       </c>
       <c r="N364" t="inlineStr">
         <is>
@@ -37902,15 +37944,19 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>received in                       convertible                                          controlling      Total equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>May 31, 2018 27,787,371 $ 6,495,964 $ - $ 708,430 $ - $ (7,275,692) $ (71,298) $</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr"/>
+          <t>Deferred income tax recovery (notes 6 and 10)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -37946,13 +37992,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L365" s="5" t="n">
-        <v>-0.071298</v>
-      </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M365" s="5" t="n">
+        <v>0.040306</v>
       </c>
       <c r="N365" t="inlineStr">
         <is>
@@ -37988,15 +38034,19 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>received in                       convertible                                          controlling      Total equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Share issuance costs - (486) - - - - (486)</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -38033,12 +38083,10 @@
         </is>
       </c>
       <c r="L366" s="5" t="n">
-        <v>-0.000486</v>
-      </c>
-      <c r="M366" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.570663</v>
+      </c>
+      <c r="M366" s="5" t="n">
+        <v>-3.040474</v>
       </c>
       <c r="N366" t="inlineStr">
         <is>
@@ -38079,7 +38127,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance - - 89,040 - - - 89,040</t>
+          <t>May 31, 2018 27,787,371 $ 6,495,964 $ - $ 708,430 $ - $ (7,275,692) $ (71,298) $</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -38119,7 +38167,7 @@
         </is>
       </c>
       <c r="L367" s="5" t="n">
-        <v>0.08903999999999999</v>
+        <v>-0.071298</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
@@ -38165,7 +38213,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - - (570,663) (570,663)</t>
+          <t>Share issuance costs - (486) - - - - (486)</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -38205,7 +38253,7 @@
         </is>
       </c>
       <c r="L368" s="5" t="n">
-        <v>-0.570663</v>
+        <v>-0.000486</v>
       </c>
       <c r="M368" t="inlineStr">
         <is>
@@ -38251,7 +38299,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>May 31, 2019 27,787,371 6,495,478 89,040 708,430 - (7,846,355) (553,407)</t>
+          <t>Subscriptions received in advance - - 89,040 - - - 89,040</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -38291,7 +38339,7 @@
         </is>
       </c>
       <c r="L369" s="5" t="n">
-        <v>-0.553407</v>
+        <v>0.08903999999999999</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -38337,7 +38385,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Private placement shares issued 55,985,462 7,358,837 (89,040) - - - 7,269,797</t>
+          <t>Loss for the year - - - - - (570,663) (570,663)</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -38377,7 +38425,7 @@
         </is>
       </c>
       <c r="L370" s="5" t="n">
-        <v>7.269797</v>
+        <v>-0.570663</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
@@ -38423,7 +38471,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Finders’ shares issued 1,041,586 208,317 - - - - 208,317</t>
+          <t>May 31, 2019 27,787,371 6,495,478 89,040 708,430 - (7,846,355) (553,407)</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -38463,7 +38511,7 @@
         </is>
       </c>
       <c r="L371" s="5" t="n">
-        <v>0.208317</v>
+        <v>-0.553407</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
@@ -38509,7 +38557,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Warrants exercised 2,365,000 283,800 - - - - 283,800</t>
+          <t>Private placement shares issued 55,985,462 7,358,837 (89,040) - - - 7,269,797</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -38549,7 +38597,7 @@
         </is>
       </c>
       <c r="L372" s="5" t="n">
-        <v>0.2838</v>
+        <v>7.269797</v>
       </c>
       <c r="M372" t="inlineStr">
         <is>
@@ -38595,7 +38643,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (189,240) - - - - (189,240)</t>
+          <t>Finders’ shares issued 1,041,586 208,317 - - - - 208,317</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -38635,7 +38683,7 @@
         </is>
       </c>
       <c r="L373" s="5" t="n">
-        <v>-0.18924</v>
+        <v>0.208317</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
@@ -38681,7 +38729,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Share issuance costs – finders’ shares - (208,317) - - - - (208,317)</t>
+          <t>Warrants exercised 2,365,000 283,800 - - - - 283,800</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -38721,7 +38769,7 @@
         </is>
       </c>
       <c r="L374" s="5" t="n">
-        <v>-0.208317</v>
+        <v>0.2838</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
@@ -38767,7 +38815,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Shares issuance costs - finders’ warrants - (90,909) - 90,909 - - -</t>
+          <t>Share issuance costs - cash - (189,240) - - - - (189,240)</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -38806,10 +38854,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L375" s="5" t="n">
+        <v>-0.18924</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
@@ -38855,7 +38901,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal (note 4) - - - - - - -</t>
+          <t>Share issuance costs – finders’ shares - (208,317) - - - - (208,317)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -38895,10 +38941,12 @@
         </is>
       </c>
       <c r="L376" s="5" t="n">
-        <v>0.443168</v>
-      </c>
-      <c r="M376" s="5" t="n">
-        <v>0.443168</v>
+        <v>-0.208317</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N376" t="inlineStr">
         <is>
@@ -38934,12 +38982,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal non-</t>
+          <t>received in                       convertible                                          controlling      Total equity</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Issuance of convertible note - - - - 149,280 - 149,280</t>
+          <t>Shares issuance costs - finders’ warrants - (90,909) - 90,909 - - -</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -38978,8 +39026,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L377" s="5" t="n">
-        <v>0.14928</v>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
@@ -39020,12 +39070,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal non-</t>
+          <t>received in                       convertible                                          controlling      Total equity</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Settlement of convertible note (net) 4,000,000 800,000 - 108,974 (108,974) - 800,000</t>
+          <t>Acquisition of Minera Cachinal (note 4) - - - - - - -</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -39065,12 +39115,10 @@
         </is>
       </c>
       <c r="L378" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.443168</v>
+      </c>
+      <c r="M378" s="5" t="n">
+        <v>0.443168</v>
       </c>
       <c r="N378" t="inlineStr">
         <is>
@@ -39111,7 +39159,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Share-based payments - - - 1,256,182 - - 1,256,182</t>
+          <t>Issuance of convertible note - - - - 149,280 - 149,280</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -39151,7 +39199,7 @@
         </is>
       </c>
       <c r="L379" s="5" t="n">
-        <v>1.256182</v>
+        <v>0.14928</v>
       </c>
       <c r="M379" t="inlineStr">
         <is>
@@ -39197,7 +39245,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Acquisition of Minera Cachinal non- total</t>
+          <t>Settlement of convertible note (net) 4,000,000 800,000 - 108,974 (108,974) - 800,000</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -39237,7 +39285,7 @@
         </is>
       </c>
       <c r="L380" s="5" t="n">
-        <v>5.831465</v>
+        <v>0.8</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
@@ -39276,10 +39324,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Acquisition of Minera Cachinal non-</t>
+        </is>
+      </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>May 31, 2019 May</t>
+          <t>Share-based payments - - - 1,256,182 - - 1,256,182</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -39313,11 +39365,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K381" s="5" t="n">
-        <v>0.002018</v>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L381" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>1.256182</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
@@ -39358,12 +39412,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Acquisition of Minera Cachinal non-</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Accounting and legal (note 6) $</t>
+          <t>Acquisition of Minera Cachinal non- total</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -39397,11 +39451,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K382" s="5" t="n">
-        <v>0.09608899999999999</v>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L382" s="5" t="n">
-        <v>0.073043</v>
+        <v>5.831465</v>
       </c>
       <c r="M382" t="inlineStr">
         <is>
@@ -39440,21 +39496,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B383" t="inlineStr"/>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Consulting (note 6)</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>May 31, 2019 May</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -39486,10 +39534,10 @@
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>0.189</v>
+        <v>0.002018</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>0.18</v>
+        <v>3.1e-05</v>
       </c>
       <c r="M383" t="inlineStr">
         <is>
@@ -39535,7 +39583,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Corporate secretarial (note 6)</t>
+          <t>Accounting and legal (note 6) $</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -39570,10 +39618,10 @@
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>0.015</v>
+        <v>0.09608899999999999</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>0.015</v>
+        <v>0.073043</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
@@ -39619,10 +39667,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Directors' fees (note 6)</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>Consulting (note 6)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -39653,13 +39705,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K385" s="5" t="n">
+        <v>0.189</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>0.027</v>
+        <v>0.18</v>
       </c>
       <c r="M385" t="inlineStr">
         <is>
@@ -39705,7 +39755,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Office and sundry (note 6)</t>
+          <t>Corporate secretarial (note 6)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -39740,10 +39790,10 @@
         </is>
       </c>
       <c r="K386" s="5" t="n">
-        <v>0.056233</v>
+        <v>0.015</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>0.100201</v>
+        <v>0.015</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
@@ -39789,10 +39839,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Property investigation (note 4)</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>Directors' fees (note 6)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -39823,11 +39877,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K387" s="5" t="n">
-        <v>0.076837</v>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L387" s="5" t="n">
-        <v>0.051547</v>
+        <v>0.027</v>
       </c>
       <c r="M387" t="inlineStr">
         <is>
@@ -39868,19 +39924,15 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Office and sundry (note 6)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -39912,10 +39964,10 @@
         </is>
       </c>
       <c r="K388" s="5" t="n">
-        <v>-0.453582</v>
+        <v>0.056233</v>
       </c>
       <c r="L388" s="5" t="n">
-        <v>-0.570663</v>
+        <v>0.100201</v>
       </c>
       <c r="M388" t="inlineStr">
         <is>
@@ -39956,19 +40008,15 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Property investigation (note 4)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -40000,10 +40048,10 @@
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.076837</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.051547</v>
       </c>
       <c r="M389" t="inlineStr">
         <is>
@@ -40049,12 +40097,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -40088,10 +40136,10 @@
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>22.515902</v>
+        <v>-0.453582</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>27.787384</v>
+        <v>-0.570663</v>
       </c>
       <c r="M390" t="inlineStr">
         <is>
@@ -40132,15 +40180,19 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Number                        Subscriptions     Share-based        currency</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>May 31, 2017 6,655,099 $ 5,089,506 - $ 708,430 $ 1,084 $</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr"/>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -40172,10 +40224,10 @@
         </is>
       </c>
       <c r="K391" s="5" t="n">
-        <v>-1.02309</v>
+        <v>-2e-08</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>-6.82211</v>
+        <v>-2e-08</v>
       </c>
       <c r="M391" t="inlineStr">
         <is>
@@ -40216,15 +40268,19 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Number                        Subscriptions     Share-based        currency</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Private placement shares issued 14,000,280 700,014 - - -</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -40256,12 +40312,10 @@
         </is>
       </c>
       <c r="K392" s="5" t="n">
-        <v>0.700014</v>
-      </c>
-      <c r="L392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>22.515902</v>
+      </c>
+      <c r="L392" s="5" t="n">
+        <v>27.787384</v>
       </c>
       <c r="M392" t="inlineStr">
         <is>
@@ -40307,7 +40361,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Shares issued for debt 7,132,005 713,201 - -</t>
+          <t>May 31, 2017 6,655,099 $ 5,089,506 - $ 708,430 $ 1,084 $</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -40342,12 +40396,10 @@
         </is>
       </c>
       <c r="K393" s="5" t="n">
-        <v>0.713201</v>
-      </c>
-      <c r="L393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.02309</v>
+      </c>
+      <c r="L393" s="5" t="n">
+        <v>-6.82211</v>
       </c>
       <c r="M393" t="inlineStr">
         <is>
@@ -40393,7 +40445,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Share issuance costs - (6,757) - - -</t>
+          <t>Private placement shares issued 14,000,280 700,014 - - -</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -40428,7 +40480,7 @@
         </is>
       </c>
       <c r="K394" s="5" t="n">
-        <v>-0.006757</v>
+        <v>0.700014</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -40479,7 +40531,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - (1,084)</t>
+          <t>Shares issued for debt 7,132,005 713,201 - -</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -40514,10 +40566,12 @@
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>-0.454666</v>
-      </c>
-      <c r="L395" s="5" t="n">
-        <v>-0.453582</v>
+        <v>0.713201</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
@@ -40563,7 +40617,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>May 31, 2018 27,787,384 6,495,964 - 708,430 -</t>
+          <t>Share issuance costs - (6,757) - - -</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -40598,10 +40652,12 @@
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>-0.071298</v>
-      </c>
-      <c r="L396" s="5" t="n">
-        <v>-7.275692</v>
+        <v>-0.006757</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
@@ -40647,7 +40703,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Share issuance costs - (486) - - -</t>
+          <t>Loss for the year - - - - (1,084)</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -40682,12 +40738,10 @@
         </is>
       </c>
       <c r="K397" s="5" t="n">
-        <v>-0.000486</v>
-      </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.454666</v>
+      </c>
+      <c r="L397" s="5" t="n">
+        <v>-0.453582</v>
       </c>
       <c r="M397" t="inlineStr">
         <is>
@@ -40733,7 +40787,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance - - 89,040 - -</t>
+          <t>May 31, 2018 27,787,384 6,495,964 - 708,430 -</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -40768,12 +40822,10 @@
         </is>
       </c>
       <c r="K398" s="5" t="n">
-        <v>0.08903999999999999</v>
-      </c>
-      <c r="L398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.071298</v>
+      </c>
+      <c r="L398" s="5" t="n">
+        <v>-7.275692</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -40819,14 +40871,10 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Loss for the year - - - - -</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs - (486) - - -</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -40858,10 +40906,12 @@
         </is>
       </c>
       <c r="K399" s="5" t="n">
-        <v>-0.570663</v>
-      </c>
-      <c r="L399" s="5" t="n">
-        <v>-0.570663</v>
+        <v>-0.000486</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M399" t="inlineStr">
         <is>
@@ -40907,7 +40957,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>May 31, 2019 27,787,384 $ 6,495,478 $ 89,040 $ 708,430 $ - $</t>
+          <t>Subscriptions received in advance - - 89,040 - -</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -40942,10 +40992,12 @@
         </is>
       </c>
       <c r="K400" s="5" t="n">
-        <v>-0.553407</v>
-      </c>
-      <c r="L400" s="5" t="n">
-        <v>-7.846355</v>
+        <v>0.08903999999999999</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M400" t="inlineStr">
         <is>
@@ -40984,13 +41036,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Number                        Subscriptions     Share-based        currency</t>
+        </is>
+      </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>May 31, 2018 May</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
+          <t>Loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -41016,16 +41076,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J401" s="5" t="n">
-        <v>0.002017</v>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.570663</v>
+      </c>
+      <c r="L401" s="5" t="n">
+        <v>-0.570663</v>
       </c>
       <c r="M401" t="inlineStr">
         <is>
@@ -41066,12 +41126,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Number                        Subscriptions     Share-based        currency</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Accounting and legal (note 7) $</t>
+          <t>May 31, 2019 27,787,384 $ 6,495,478 $ 89,040 $ 708,430 $ - $</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -41095,19 +41155,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I402" s="5" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="J402" s="5" t="n">
-        <v>0.071418</v>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>0.09608899999999999</v>
-      </c>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.553407</v>
+      </c>
+      <c r="L402" s="5" t="n">
+        <v>-7.846355</v>
       </c>
       <c r="M402" t="inlineStr">
         <is>
@@ -41146,21 +41208,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Consulting (note 7)</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>May 31, 2018 May</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -41187,10 +41241,10 @@
         </is>
       </c>
       <c r="J403" s="5" t="n">
-        <v>0.144</v>
+        <v>0.002017</v>
       </c>
       <c r="K403" s="5" t="n">
-        <v>0.189</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
@@ -41241,7 +41295,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Corporate secretarial (note 7)</t>
+          <t>Accounting and legal (note 7) $</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -41266,13 +41320,13 @@
         </is>
       </c>
       <c r="I404" s="5" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="J404" s="5" t="n">
-        <v>0.015</v>
+        <v>0.071418</v>
       </c>
       <c r="K404" s="5" t="n">
-        <v>0.015</v>
+        <v>0.09608899999999999</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -41323,10 +41377,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Office and sundry (note 7)</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr"/>
+          <t>Consulting (note 7)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -41347,14 +41405,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I405" s="5" t="n">
-        <v>0.018534</v>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J405" s="5" t="n">
-        <v>0.023528</v>
+        <v>0.144</v>
       </c>
       <c r="K405" s="5" t="n">
-        <v>0.056233</v>
+        <v>0.189</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -41405,7 +41465,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>Corporate secretarial (note 7)</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -41429,18 +41489,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I406" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J406" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="K406" s="5" t="n">
-        <v>0.076837</v>
+        <v>0.015</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -41491,7 +41547,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Gain on forfeiture of deposit (note 4)</t>
+          <t>Office and sundry (note 7)</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -41516,15 +41572,13 @@
         </is>
       </c>
       <c r="I407" s="5" t="n">
-        <v>0.010014</v>
+        <v>0.018534</v>
       </c>
       <c r="J407" s="5" t="n">
-        <v>0.004488</v>
-      </c>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023528</v>
+      </c>
+      <c r="K407" s="5" t="n">
+        <v>0.056233</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -41575,14 +41629,10 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property investigation</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -41603,14 +41653,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I408" s="5" t="n">
-        <v>-0.190441</v>
-      </c>
-      <c r="J408" s="5" t="n">
-        <v>-0.280277</v>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K408" s="5" t="n">
-        <v>-0.453582</v>
+        <v>0.076837</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -41656,12 +41710,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
+          <t>Gain on forfeiture of deposit (note 4)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -41680,17 +41734,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H409" s="5" t="n">
-        <v>-0.005286</v>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I409" s="5" t="n">
-        <v>0.001485</v>
+        <v>0.010014</v>
       </c>
       <c r="J409" s="5" t="n">
-        <v>-9.8e-05</v>
-      </c>
-      <c r="K409" s="5" t="n">
-        <v>-0.001084</v>
+        <v>0.004488</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -41736,12 +41794,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -41769,16 +41827,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I410" s="5" t="n">
+        <v>-0.190441</v>
       </c>
       <c r="J410" s="5" t="n">
-        <v>-0.280375</v>
+        <v>-0.280277</v>
       </c>
       <c r="K410" s="5" t="n">
-        <v>-0.454666</v>
+        <v>-0.453582</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -41829,14 +41885,10 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -41847,22 +41899,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G411" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H411" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005286</v>
+      </c>
+      <c r="I411" s="5" t="n">
+        <v>0.001485</v>
       </c>
       <c r="J411" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-9.8e-05</v>
       </c>
       <c r="K411" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.001084</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -41913,12 +41965,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -41947,10 +41999,10 @@
         </is>
       </c>
       <c r="J412" s="5" t="n">
-        <v>6.655099</v>
+        <v>-0.280375</v>
       </c>
       <c r="K412" s="5" t="n">
-        <v>14.066657</v>
+        <v>-0.454666</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -41996,15 +42048,19 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>reserve          reserve            Deficit           deficiency</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>May 31, 2016 6,655,099 $ 5,089,506 $ 708,430 $ 1,182 $</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr"/>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -42015,15 +42071,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G413" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -42031,10 +42083,10 @@
         </is>
       </c>
       <c r="J413" s="5" t="n">
-        <v>-0.742715</v>
+        <v>-4e-08</v>
       </c>
       <c r="K413" s="5" t="n">
-        <v>-6.541833</v>
+        <v>-3e-08</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -42080,17 +42132,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>reserve          reserve            Deficit           deficiency</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (98)</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -42113,14 +42165,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I414" s="5" t="n">
-        <v>-0.280375</v>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J414" s="5" t="n">
-        <v>-0.280375</v>
+        <v>6.655099</v>
       </c>
       <c r="K414" s="5" t="n">
-        <v>-0.280277</v>
+        <v>14.066657</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -42171,7 +42225,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>May 31, 2017 6,655,099 5,089,506 708,430 1,084</t>
+          <t>May 31, 2016 6,655,099 $ 5,089,506 $ 708,430 $ 1,182 $</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -42201,10 +42255,10 @@
         </is>
       </c>
       <c r="J415" s="5" t="n">
-        <v>-1.02309</v>
+        <v>-0.742715</v>
       </c>
       <c r="K415" s="5" t="n">
-        <v>-6.82211</v>
+        <v>-6.541833</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -42255,10 +42309,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Private placement shares issued 14,000,280 700,014 - -</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr"/>
+          <t>Loss for the year - - - (98)</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -42279,18 +42337,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I416" s="5" t="n">
+        <v>-0.280375</v>
       </c>
       <c r="J416" s="5" t="n">
-        <v>0.700014</v>
-      </c>
-      <c r="K416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.280375</v>
+      </c>
+      <c r="K416" s="5" t="n">
+        <v>-0.280277</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -42341,7 +42395,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Shares issued for debt 7,132,005 713,201 - -</t>
+          <t>May 31, 2017 6,655,099 5,089,506 708,430 1,084</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -42371,12 +42425,10 @@
         </is>
       </c>
       <c r="J417" s="5" t="n">
-        <v>0.713201</v>
-      </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.02309</v>
+      </c>
+      <c r="K417" s="5" t="n">
+        <v>-6.82211</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -42427,7 +42479,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Share issuance costs - (6,757) - -</t>
+          <t>Private placement shares issued 14,000,280 700,014 - -</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -42457,7 +42509,7 @@
         </is>
       </c>
       <c r="J418" s="5" t="n">
-        <v>-0.006757</v>
+        <v>0.700014</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
@@ -42513,7 +42565,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Loss for the year - - - (1,084)</t>
+          <t>Shares issued for debt 7,132,005 713,201 - -</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -42543,10 +42595,12 @@
         </is>
       </c>
       <c r="J419" s="5" t="n">
-        <v>-0.454666</v>
-      </c>
-      <c r="K419" s="5" t="n">
-        <v>-0.453582</v>
+        <v>0.713201</v>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -42597,7 +42651,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>May 31, 2018 27,787,384 $ 6,495,964 $ 708,430 $ - $</t>
+          <t>Share issuance costs - (6,757) - -</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -42627,10 +42681,12 @@
         </is>
       </c>
       <c r="J420" s="5" t="n">
-        <v>-0.071298</v>
-      </c>
-      <c r="K420" s="5" t="n">
-        <v>-7.275692</v>
+        <v>-0.006757</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -42674,10 +42730,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>reserve          reserve            Deficit           deficiency</t>
+        </is>
+      </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>May 31, 2017 May</t>
+          <t>Loss for the year - - - (1,084)</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -42701,16 +42761,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I421" s="5" t="n">
-        <v>0.002016</v>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J421" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.454666</v>
+      </c>
+      <c r="K421" s="5" t="n">
+        <v>-0.453582</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -42756,12 +42816,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>reserve          reserve            Deficit           deficiency</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Consulting - related party (note 7)</t>
+          <t>May 31, 2018 27,787,384 $ 6,495,964 $ 708,430 $ - $</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -42785,16 +42845,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I422" s="5" t="n">
-        <v>0.144</v>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J422" s="5" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="K422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.071298</v>
+      </c>
+      <c r="K422" s="5" t="n">
+        <v>-7.275692</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -42838,40 +42898,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>May 31, 2017 May</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F423" s="5" t="n">
-        <v>0.00155</v>
-      </c>
-      <c r="G423" s="5" t="n">
-        <v>0.001938</v>
-      </c>
-      <c r="H423" s="5" t="n">
-        <v>0.001444</v>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I423" s="5" t="n">
-        <v>0.000276</v>
+        <v>0.002016</v>
       </c>
       <c r="J423" s="5" t="n">
-        <v>0.000153</v>
+        <v>3.1e-05</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
@@ -42922,19 +42980,15 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Consulting - related party (note 7)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -42956,10 +43010,10 @@
         </is>
       </c>
       <c r="I424" s="5" t="n">
-        <v>-0.188956</v>
+        <v>0.144</v>
       </c>
       <c r="J424" s="5" t="n">
-        <v>-0.280375</v>
+        <v>0.144</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
@@ -43010,17 +43064,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Interest and bank charges</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -43028,26 +43082,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F425" s="5" t="n">
+        <v>0.00155</v>
+      </c>
+      <c r="G425" s="5" t="n">
+        <v>0.001938</v>
+      </c>
+      <c r="H425" s="5" t="n">
+        <v>0.001444</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.000276</v>
       </c>
       <c r="J425" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.000153</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
@@ -43098,17 +43146,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -43116,20 +43164,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F426" s="5" t="n">
-        <v>30.125807</v>
-      </c>
-      <c r="G426" s="5" t="n">
-        <v>36.061197</v>
-      </c>
-      <c r="H426" s="5" t="n">
-        <v>43.648197</v>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I426" s="5" t="n">
-        <v>6.655099</v>
+        <v>-0.188956</v>
       </c>
       <c r="J426" s="5" t="n">
-        <v>6.655099</v>
+        <v>-0.280375</v>
       </c>
       <c r="K426" t="inlineStr">
         <is>
@@ -43180,15 +43234,19 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>reserve          reserve            Deficit           deficiency</t>
+          <t>Loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>May 31, 2015 6,655,099 $ 5,089,506 $ 708,430 $ (303) $</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr"/>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -43210,10 +43268,10 @@
         </is>
       </c>
       <c r="I427" s="5" t="n">
-        <v>-0.553759</v>
+        <v>-3e-08</v>
       </c>
       <c r="J427" s="5" t="n">
-        <v>-6.351392</v>
+        <v>-4e-08</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
@@ -43264,17 +43322,17 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>reserve          reserve            Deficit           deficiency</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Loss for the year - - - 1,485</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -43282,26 +43340,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F428" s="5" t="n">
+        <v>30.125807</v>
+      </c>
+      <c r="G428" s="5" t="n">
+        <v>36.061197</v>
+      </c>
+      <c r="H428" s="5" t="n">
+        <v>43.648197</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>-0.188956</v>
+        <v>6.655099</v>
       </c>
       <c r="J428" s="5" t="n">
-        <v>-0.190441</v>
+        <v>6.655099</v>
       </c>
       <c r="K428" t="inlineStr">
         <is>
@@ -43357,7 +43409,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>May 31, 2016 6,655,099 5,089,506 708,430 1,182</t>
+          <t>May 31, 2015 6,655,099 $ 5,089,506 $ 708,430 $ (303) $</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -43382,10 +43434,10 @@
         </is>
       </c>
       <c r="I429" s="5" t="n">
-        <v>-0.742715</v>
+        <v>-0.553759</v>
       </c>
       <c r="J429" s="5" t="n">
-        <v>-6.541833</v>
+        <v>-6.351392</v>
       </c>
       <c r="K429" t="inlineStr">
         <is>
@@ -43441,10 +43493,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>May 31, 2017 6,655,099 $ 5,089,506 $ 708,430 $ 1,084 $</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr"/>
+          <t>Loss for the year - - - 1,485</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -43466,10 +43522,10 @@
         </is>
       </c>
       <c r="I430" s="5" t="n">
-        <v>-1.02309</v>
+        <v>-0.188956</v>
       </c>
       <c r="J430" s="5" t="n">
-        <v>-6.82211</v>
+        <v>-0.190441</v>
       </c>
       <c r="K430" t="inlineStr">
         <is>
@@ -43518,10 +43574,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr"/>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>reserve          reserve            Deficit           deficiency</t>
+        </is>
+      </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>May 31, 2014 May</t>
+          <t>May 31, 2016 6,655,099 5,089,506 708,430 1,182</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -43535,21 +43595,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G431" s="5" t="n">
-        <v>0.002013</v>
-      </c>
-      <c r="H431" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>-0.742715</v>
+      </c>
+      <c r="J431" s="5" t="n">
+        <v>-6.541833</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
@@ -43600,36 +43660,40 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>reserve          reserve            Deficit           deficiency</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Accounting and audit $</t>
+          <t>May 31, 2017 6,655,099 $ 5,089,506 $ 708,430 $ 1,084 $</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
-      <c r="E432" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F432" s="5" t="n">
-        <v>0.061143</v>
-      </c>
-      <c r="G432" s="5" t="n">
-        <v>0.062933</v>
-      </c>
-      <c r="H432" s="5" t="n">
-        <v>0.06568</v>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I432" s="5" t="n">
+        <v>-1.02309</v>
+      </c>
+      <c r="J432" s="5" t="n">
+        <v>-6.82211</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
@@ -43678,14 +43742,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Business development</t>
+          <t>May 31, 2014 May</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -43694,16 +43754,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F433" s="5" t="n">
-        <v>0.08799999999999999</v>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G433" s="5" t="n">
-        <v>0.00515</v>
-      </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002013</v>
+      </c>
+      <c r="H433" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -43769,23 +43829,21 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Consulting - related party</t>
+          <t>Accounting and audit $</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E434" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="F434" s="5" t="n">
-        <v>0.1525</v>
+        <v>0.061143</v>
       </c>
       <c r="G434" s="5" t="n">
-        <v>0.09</v>
+        <v>0.062933</v>
       </c>
       <c r="H434" s="5" t="n">
-        <v>0.05425</v>
+        <v>0.06568</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -43851,7 +43909,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Corporate secretarial</t>
+          <t>Business development</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -43861,13 +43919,15 @@
         </is>
       </c>
       <c r="F435" s="5" t="n">
-        <v>0.01375</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G435" s="5" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="H435" s="5" t="n">
-        <v>0.014</v>
+        <v>0.00515</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -43933,7 +43993,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Directors' fees</t>
+          <t>Consulting - related party</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -43943,13 +44003,13 @@
         </is>
       </c>
       <c r="F436" s="5" t="n">
-        <v>0.054</v>
+        <v>0.1525</v>
       </c>
       <c r="G436" s="5" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H436" s="5" t="n">
-        <v>0.004</v>
+        <v>0.05425</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -44015,25 +44075,23 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E437" s="5" t="n">
-        <v>0.006002</v>
+          <t>Corporate secretarial</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F437" s="5" t="n">
-        <v>0.022537</v>
+        <v>0.01375</v>
       </c>
       <c r="G437" s="5" t="n">
-        <v>0.020055</v>
+        <v>0.0155</v>
       </c>
       <c r="H437" s="5" t="n">
-        <v>0.003175</v>
+        <v>0.014</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -44099,23 +44157,27 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Office and sundry</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr"/>
+          <t>Directors' fees</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F438" s="5" t="n">
-        <v>0.113726</v>
+        <v>0.054</v>
       </c>
       <c r="G438" s="5" t="n">
-        <v>0.08655599999999999</v>
+        <v>0.03</v>
       </c>
       <c r="H438" s="5" t="n">
-        <v>0.118838</v>
+        <v>0.004</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -44181,23 +44243,25 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Salaries and employee benefits</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr"/>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E439" s="5" t="n">
+        <v>0.006002</v>
       </c>
       <c r="F439" s="5" t="n">
-        <v>0.222138</v>
+        <v>0.022537</v>
       </c>
       <c r="G439" s="5" t="n">
-        <v>0.15093</v>
+        <v>0.020055</v>
       </c>
       <c r="H439" s="5" t="n">
-        <v>0.014368</v>
+        <v>0.003175</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -44263,7 +44327,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Share-based payments (note 6(d))</t>
+          <t>Office and sundry</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -44273,13 +44337,13 @@
         </is>
       </c>
       <c r="F440" s="5" t="n">
-        <v>0.550939</v>
+        <v>0.113726</v>
       </c>
       <c r="G440" s="5" t="n">
-        <v>0.027585</v>
+        <v>0.08655599999999999</v>
       </c>
       <c r="H440" s="5" t="n">
-        <v>0.015989</v>
+        <v>0.118838</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -44340,12 +44404,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Other items (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Recovery of accounts payable</t>
+          <t>Salaries and employee benefits</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
@@ -44354,18 +44418,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F441" s="5" t="n">
+        <v>0.222138</v>
+      </c>
+      <c r="G441" s="5" t="n">
+        <v>0.15093</v>
       </c>
       <c r="H441" s="5" t="n">
-        <v>0.08574900000000001</v>
+        <v>0.014368</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -44426,12 +44486,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Other items (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Write-off of resource property costs</t>
+          <t>Share-based payments (note 6(d))</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -44440,18 +44500,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F442" s="5" t="n">
+        <v>0.550939</v>
+      </c>
+      <c r="G442" s="5" t="n">
+        <v>0.027585</v>
       </c>
       <c r="H442" s="5" t="n">
-        <v>-0.590168</v>
+        <v>0.015989</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -44517,14 +44573,10 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Recovery of accounts payable</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr">
         <is>
           <t>-</t>
@@ -44535,11 +44587,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G443" s="5" t="n">
-        <v>-1.147721</v>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H443" s="5" t="n">
-        <v>-1.057731</v>
+        <v>0.08574900000000001</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -44600,19 +44654,15 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items (expense)</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of resource property costs</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -44623,11 +44673,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G444" s="5" t="n">
-        <v>-1.147721</v>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H444" s="5" t="n">
-        <v>-1.063017</v>
+        <v>-0.590168</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -44686,28 +44738,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr"/>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Other items (expense)</t>
+        </is>
+      </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>May 31, 2013 May</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F445" s="5" t="n">
-        <v>0.002012</v>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G445" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.147721</v>
+      </c>
+      <c r="H445" s="5" t="n">
+        <v>-1.057731</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -44768,12 +44828,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Total loss and comprehensive loss</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Total loss and comprehensive loss for the year $</t>
+          <t>Total comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -44786,16 +44846,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F446" s="5" t="n">
-        <v>-2.620374</v>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G446" s="5" t="n">
         <v>-1.147721</v>
       </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H446" s="5" t="n">
+        <v>-1.063017</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -44854,31 +44914,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>Total loss and comprehensive loss</t>
-        </is>
-      </c>
+      <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>May 31, 2013 May</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F447" s="5" t="n">
-        <v>-9e-08</v>
+        <v>0.002012</v>
       </c>
       <c r="G447" s="5" t="n">
-        <v>-3e-08</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
@@ -44944,29 +44996,29 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Total loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>(7,492)                                                                                                                        27,585 240,000 30,000                                               equity          (31,001)                        550,939 (188,730)                                                                                                                                                                1,375,564                                                                                                               2,200,000 1,464,730                         (2,620,374)                                                      517,936                                                                                                                                                                                                                                                                             (1,147,721)                                       Total</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr"/>
+          <t>Total loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F448" s="5" t="n">
+        <v>-2.620374</v>
+      </c>
+      <c r="G448" s="5" t="n">
+        <v>-1.147721</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
@@ -45032,25 +45084,29 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Weighted average number</t>
+          <t>Total loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Deficit (31,002) (2,620,374) (2,651,376)</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr"/>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F449" s="5" t="n">
-        <v>-3.799097</v>
+        <v>-9e-08</v>
       </c>
       <c r="G449" s="5" t="n">
-        <v>-1.147721</v>
+        <v>-3e-08</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
@@ -45121,7 +45177,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Weighted average number total</t>
+          <t>(7,492)                                                                                                                        27,585 240,000 30,000                                               equity          (31,001)                        550,939 (188,730)                                                                                                                                                                1,375,564                                                                                                               2,200,000 1,464,730                         (2,620,374)                                                      517,936                                                                                                                                                                                                                                                                             (1,147,721)                                       Total</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
@@ -45130,11 +45186,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F450" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G450" s="5" t="n">
-        <v>6e-06</v>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
@@ -45205,7 +45265,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Share-based payments reserve 550,939 550,939</t>
+          <t>Deficit (31,002) (2,620,374) (2,651,376)</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -45215,10 +45275,10 @@
         </is>
       </c>
       <c r="F451" s="5" t="n">
-        <v>0.578524</v>
+        <v>-3.799097</v>
       </c>
       <c r="G451" s="5" t="n">
-        <v>0.027585</v>
+        <v>-1.147721</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
@@ -45289,7 +45349,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>4 30,000 (7,492) capital (note (188,730) 240,000 2,200,000 1,464,730</t>
+          <t>Weighted average number total</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -45299,10 +45359,10 @@
         </is>
       </c>
       <c r="F452" s="5" t="n">
-        <v>3.738509</v>
+        <v>1e-06</v>
       </c>
       <c r="G452" s="5" t="n">
-        <v>3.476001</v>
+        <v>6e-06</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
@@ -45368,12 +45428,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Share total</t>
+          <t>Share-based payments reserve 550,939 550,939</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -45383,10 +45443,10 @@
         </is>
       </c>
       <c r="F453" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.578524</v>
       </c>
       <c r="G453" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.027585</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
@@ -45452,25 +45512,25 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>Weighted average number</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Share</t>
+          <t>4 30,000 (7,492) capital (note (188,730) 240,000 2,200,000 1,464,730</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
-      <c r="E454" s="5" t="n">
-        <v>1e-06</v>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F454" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.738509</v>
+      </c>
+      <c r="G454" s="5" t="n">
+        <v>3.476001</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
@@ -45536,25 +45596,25 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>incorporation on</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>May 31, 2012 May</t>
+          <t>Share total</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
-      <c r="E455" s="5" t="n">
-        <v>0.002011</v>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F455" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-06</v>
+      </c>
+      <c r="G455" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="H455" t="inlineStr">
         <is>
@@ -45620,22 +45680,20 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Directors fees</t>
+          <t>Share</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E456" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F456" s="5" t="n">
-        <v>0.054</v>
+        <v>1e-06</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -45706,24 +45764,20 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>incorporation on</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Total loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>May 31, 2012 May</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" s="5" t="n">
-        <v>-0.031002</v>
+        <v>0.002011</v>
       </c>
       <c r="F457" s="5" t="n">
-        <v>-2.620374</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -45799,19 +45853,21 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
+          <t>Directors fees</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E458" s="5" t="n">
-        <v>-0.031002</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F458" s="5" t="n">
-        <v>-9e-08</v>
+        <v>0.054</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -45887,19 +45943,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>equity 1 (31,002) (31,001)        550,939                     (188,730)                                                                                                                                            2,200,000 1,464,730                                                                                                                                                                                                                (2,620,374) 1,375,564                                       Total</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr"/>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E459" s="5" t="n">
+        <v>-0.031002</v>
+      </c>
+      <c r="F459" s="5" t="n">
+        <v>-2.620374</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -45975,15 +46031,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Deficit (31,002) (31,002)</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr"/>
+          <t>Loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E460" s="5" t="n">
-        <v>-2.651376</v>
+        <v>-0.031002</v>
       </c>
       <c r="F460" s="5" t="n">
-        <v>-2.620374</v>
+        <v>-9e-08</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -46059,15 +46119,19 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Share-based payments reserve</t>
+          <t>equity 1 (31,002) (31,001)        550,939                     (188,730)                                                                                                                                            2,200,000 1,464,730                                                                                                                                                                                                                (2,620,374) 1,375,564                                       Total</t>
         </is>
       </c>
       <c r="D461" t="inlineStr"/>
-      <c r="E461" s="5" t="n">
-        <v>0.550939</v>
-      </c>
-      <c r="F461" s="5" t="n">
-        <v>0.550939</v>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -46143,72 +46207,420 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>4 capital (note (188,730) 2,200,000</t>
+          <t>Deficit (31,002) (31,002)</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
       <c r="E462" s="5" t="n">
+        <v>-2.651376</v>
+      </c>
+      <c r="F462" s="5" t="n">
+        <v>-2.620374</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Share-based payments reserve</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" s="5" t="n">
+        <v>0.550939</v>
+      </c>
+      <c r="F463" s="5" t="n">
+        <v>0.550939</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>4 capital (note (188,730) 2,200,000</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" s="5" t="n">
         <v>3.476001</v>
       </c>
-      <c r="F462" s="5" t="n">
+      <c r="F464" s="5" t="n">
         <v>1.46473</v>
       </c>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R462" t="inlineStr">
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="n">
+        <v>0.031002</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E466" s="5" t="n">
+        <v>-0.031002</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
         <is>
           <t>-</t>
         </is>
